--- a/capabilities_checklist_completed.xlsx
+++ b/capabilities_checklist_completed.xlsx
@@ -1590,7 +1590,7 @@
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — arbitrage_catalog.py — catalog row #57 airdrop/incentive (proxy scoring)</t>
+          <t>مبني وشغال فعليًا — bd_platform.legal_commercial_layer.get_footer_disclosure_57 + tests/test_legal_retail_batch57_66.py</t>
         </is>
       </c>
     </row>
@@ -1650,7 +1650,7 @@
       </c>
       <c r="D61" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — data_sources_registry.py + exchange connectors (تغطية جزئية)</t>
+          <t>مبني وشغال فعليًا — bd_platform.legal_commercial_layer.pricing_transparency_manifest_60 + tests/test_legal_retail_batch57_66.py</t>
         </is>
       </c>
     </row>
@@ -1670,7 +1670,7 @@
       </c>
       <c r="D62" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — platform_api.py</t>
+          <t>مبني وشغال فعليًا — bd_platform.legal_commercial_layer.run_legal_commercial_e2e_57_61 + tests/test_legal_retail_batch57_66.py</t>
         </is>
       </c>
     </row>
@@ -1690,7 +1690,7 @@
       </c>
       <c r="D63" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — bd_platform/intelligence_market_extensions_layer.py</t>
+          <t>مبني وشغال فعليًا — bd_platform.retail_intelligence_layer.build_daily_top3_62 + tests/test_legal_retail_batch57_66.py</t>
         </is>
       </c>
     </row>
@@ -1730,7 +1730,7 @@
       </c>
       <c r="D65" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — dashboard.py</t>
+          <t>مبني وشغال فعليًا — bd_platform.retail_intelligence_layer.glossary_manifest_64 + tests/test_legal_retail_batch57_66.py</t>
         </is>
       </c>
     </row>
@@ -1770,7 +1770,7 @@
       </c>
       <c r="D67" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — platform_api.py</t>
+          <t>مبني وشغال فعليًا — bd_platform.retail_intelligence_layer.run_retail_intelligence_e2e_62_66 + tests/test_legal_retail_batch57_66.py</t>
         </is>
       </c>
     </row>
@@ -1790,7 +1790,7 @@
       </c>
       <c r="D68" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — bd_platform/arbitrage_portfolio_ux_layer.py</t>
+          <t>مبني وشغال فعليًا — bd_platform.pro_trader_layer.health_score_from_holdings_67 + tests/test_pro_trader_batch67_76.py</t>
         </is>
       </c>
     </row>
@@ -1890,7 +1890,7 @@
       </c>
       <c r="D73" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — transfer_intent_probability.py — de-peg probability index (analytical)</t>
+          <t>مبني وشغال فعليًا — bd_platform.pro_trader_layer.classify_onchain_signal_72 + tests/test_pro_trader_batch67_76.py</t>
         </is>
       </c>
     </row>
@@ -1930,7 +1930,7 @@
       </c>
       <c r="D75" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — bd_platform/intelligence_market_extensions_layer.py</t>
+          <t>مبني وشغال فعليًا — bd_platform.pro_trader_layer.run_backtest_74 + tests/test_pro_trader_batch67_76.py</t>
         </is>
       </c>
     </row>
@@ -1950,7 +1950,7 @@
       </c>
       <c r="D76" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — platform_api.py</t>
+          <t>مبني وشغال فعليًا — bd_platform.pro_trader_layer.evaluate_flexible_alert_75 + tests/test_pro_trader_batch67_76.py</t>
         </is>
       </c>
     </row>
@@ -1970,7 +1970,7 @@
       </c>
       <c r="D77" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — bd_platform/onchain_advanced.py</t>
+          <t>مبني وشغال فعليًا — bd_platform.pro_trader_layer.run_pro_trader_e2e_67_76 + tests/test_pro_trader_batch67_76.py</t>
         </is>
       </c>
     </row>
@@ -2050,7 +2050,7 @@
       </c>
       <c r="D81" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — institutional handler surfaces</t>
+          <t>مبني وشغال فعليًا — bd_platform.whales_institutional_layer.build_exchange_health_80 + tests/test_whales_institutional_batch77_86.py</t>
         </is>
       </c>
     </row>
@@ -2070,7 +2070,7 @@
       </c>
       <c r="D82" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — bd_platform/onchain_hub.py + onchain_tracker.py + free_tier_capabilities</t>
+          <t>مبني وشغال فعليًا — bd_platform.whales_institutional_layer.build_unified_portfolio_view_81 + tests/test_whales_institutional_batch77_86.py</t>
         </is>
       </c>
     </row>
@@ -2090,7 +2090,7 @@
       </c>
       <c r="D83" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — bd_platform/security_trust_data_layer.py</t>
+          <t>مبني وشغال فعليًا — bd_platform.whales_institutional_layer.evaluate_liquidation_alert_82 + tests/test_whales_institutional_batch77_86.py</t>
         </is>
       </c>
     </row>
@@ -2110,7 +2110,7 @@
       </c>
       <c r="D84" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — platform_api.py</t>
+          <t>مبني وشغال فعليًا — bd_platform.whales_institutional_layer.smb_institution_status_83 + tests/test_whales_institutional_batch77_86.py</t>
         </is>
       </c>
     </row>
@@ -2170,7 +2170,7 @@
       </c>
       <c r="D87" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — bd_platform/onchain_hub.py + onchain_tracker.py + free_tier_capabilities</t>
+          <t>مبني وشغال فعليًا — bd_platform.whales_institutional_layer.run_whales_institutional_e2e_77_86 + tests/test_whales_institutional_batch77_86.py</t>
         </is>
       </c>
     </row>
@@ -2230,7 +2230,7 @@
       </c>
       <c r="D90" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — defi_arbitrage_engine.py + bd_platform/onchain_hub.py</t>
+          <t>مبني وشغال فعليًا — bd_platform.institutional_b2b_layer.sla_status_89 + tests/test_institutional_b2b_batch87_94.py</t>
         </is>
       </c>
     </row>
@@ -2250,7 +2250,7 @@
       </c>
       <c r="D91" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — defi_arbitrage_engine.py + bd_platform/onchain_hub.py</t>
+          <t>مبني وشغال فعليًا — bd_platform.institutional_b2b_layer.white_label_status_90 + tests/test_institutional_b2b_batch87_94.py</t>
         </is>
       </c>
     </row>
@@ -2270,7 +2270,7 @@
       </c>
       <c r="D92" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — defi_arbitrage_engine.py + bd_platform/onchain_hub.py</t>
+          <t>مبني وشغال فعليًا — bd_platform.institutional_b2b_layer.compute_vwap_deviation_91 + tests/test_institutional_b2b_batch87_94.py</t>
         </is>
       </c>
     </row>
@@ -2290,7 +2290,7 @@
       </c>
       <c r="D93" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — bd_platform/onchain_hub.py + market_context stablecoin handling</t>
+          <t>مبني وشغال فعليًا — bd_platform.institutional_b2b_layer.build_exchange_health_with_counterparty_92 + tests/test_institutional_b2b_batch87_94.py</t>
         </is>
       </c>
     </row>
@@ -2330,7 +2330,7 @@
       </c>
       <c r="D95" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — bd_platform/derivatives_hub.py long_short metrics</t>
+          <t>مبني وشغال فعليًا — bd_platform.institutional_b2b_layer.run_institutional_b2b_e2e_87_94 + tests/test_institutional_b2b_batch87_94.py</t>
         </is>
       </c>
     </row>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="D96" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — platform_api.py</t>
+          <t>مبني وشغال فعليًا — bd_platform.infra_intelligence_layer.build_admin_analytics_dashboard_95 + tests/test_infra_intelligence_batch95_104.py</t>
         </is>
       </c>
     </row>
@@ -2370,7 +2370,7 @@
       </c>
       <c r="D97" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — platform_api.py</t>
+          <t>مبني وشغال فعليًا — bd_platform.infra_intelligence_layer.enqueue_stream_event_96 + tests/test_infra_intelligence_batch95_104.py</t>
         </is>
       </c>
     </row>
@@ -2490,7 +2490,7 @@
       </c>
       <c r="D103" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — bd_platform/onchain_hub.py + market_context stablecoin handling</t>
+          <t>مبني وشغال فعليًا — bd_platform.infra_intelligence_layer.compute_il_vulnerability_102 + tests/test_infra_intelligence_batch95_104.py</t>
         </is>
       </c>
     </row>
@@ -2590,7 +2590,7 @@
       </c>
       <c r="D108" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — arbitrage_engine.py + intelligence_analysis_layer #153</t>
+          <t>مبني وشغال فعليًا — bd_platform.market_analysis_layer.compute_whale_retail_ratio_107 + tests/test_market_analysis_batch105_116.py</t>
         </is>
       </c>
     </row>
@@ -2690,7 +2690,7 @@
       </c>
       <c r="D113" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — defi_arbitrage_engine.py + bd_platform/onchain_hub.py</t>
+          <t>مبني وشغال فعليًا — bd_platform.market_analysis_layer.compute_gcli_112 + tests/test_market_analysis_batch105_116.py</t>
         </is>
       </c>
     </row>
@@ -2730,7 +2730,7 @@
       </c>
       <c r="D115" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — platform_api.py</t>
+          <t>مبني وشغال فعليًا — bd_platform.market_analysis_layer.attach_market_health_bundle_106_112_114 + tests/test_market_analysis_batch105_116.py</t>
         </is>
       </c>
     </row>
@@ -2770,7 +2770,7 @@
       </c>
       <c r="D117" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — dashboard.py</t>
+          <t>مبني وشغال فعليًا — bd_platform.market_analysis_layer.run_market_analysis_e2e_105_116 + tests/test_market_analysis_batch105_116.py</t>
         </is>
       </c>
     </row>
@@ -2830,7 +2830,7 @@
       </c>
       <c r="D120" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — institutional_assurance.py + uptime_probe_loop + centralized logs</t>
+          <t>مبني وشغال فعليًا — bd_platform.advanced_ta_risk_layer.gas_spike_alert_119 + tests/test_advanced_ta_risk_batch117_128.py</t>
         </is>
       </c>
     </row>
@@ -2910,7 +2910,7 @@
       </c>
       <c r="D124" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — audience_routing.py — risk curation routing rules</t>
+          <t>مبني وشغال فعليًا — bd_platform.advanced_ta_risk_layer.compute_volume_profile_poc_123 + tests/test_advanced_ta_risk_batch117_128.py</t>
         </is>
       </c>
     </row>
@@ -2930,7 +2930,7 @@
       </c>
       <c r="D125" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — platform_api.py</t>
+          <t>مبني وشغال فعليًا — bd_platform.advanced_ta_risk_layer.detect_fair_value_gaps_124 + tests/test_advanced_ta_risk_batch117_128.py</t>
         </is>
       </c>
     </row>
@@ -2950,7 +2950,7 @@
       </c>
       <c r="D126" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — bd_platform/roadmap_audit.py</t>
+          <t>مبني وشغال فعليًا — bd_platform.advanced_ta_risk_layer.custody_tracking_status_125 + tests/test_advanced_ta_risk_batch117_128.py</t>
         </is>
       </c>
     </row>
@@ -2970,7 +2970,7 @@
       </c>
       <c r="D127" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — مفهوم عام؛ أسطح فرعية: platform_api.py, dashboard.py</t>
+          <t>مبني وشغال فعليًا — bd_platform.advanced_ta_risk_layer.dex_front_running_risk_126 + tests/test_advanced_ta_risk_batch117_128.py</t>
         </is>
       </c>
     </row>
@@ -2990,7 +2990,7 @@
       </c>
       <c r="D128" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — bd_platform/news_classifier.py + market_event_library.py</t>
+          <t>مبني وشغال فعليًا — bd_platform.advanced_ta_risk_layer.orderbook_inefficiency_insight_127 + tests/test_advanced_ta_risk_batch117_128.py</t>
         </is>
       </c>
     </row>
@@ -3010,7 +3010,7 @@
       </c>
       <c r="D129" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — defi_arbitrage_engine.py + bd_platform/onchain_hub.py</t>
+          <t>مبني وشغال فعليًا — bd_platform.advanced_ta_risk_layer.run_advanced_ta_risk_e2e_117_128 + tests/test_advanced_ta_risk_batch117_128.py</t>
         </is>
       </c>
     </row>
@@ -3050,7 +3050,7 @@
       </c>
       <c r="D131" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — platform_api.py</t>
+          <t>مبني وشغال فعليًا — bd_platform.onchain_platform_layer.transaction_risk_insight_130 + tests/test_onchain_platform_batch129_139.py</t>
         </is>
       </c>
     </row>
@@ -3070,7 +3070,7 @@
       </c>
       <c r="D132" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — platform_api.py</t>
+          <t>مبني وشغال فعليًا — bd_platform.onchain_platform_layer.analyze_dust_assets_131 + tests/test_onchain_platform_batch129_139.py</t>
         </is>
       </c>
     </row>
@@ -3090,7 +3090,7 @@
       </c>
       <c r="D133" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — bd_platform/whales_institutional_layer.py</t>
+          <t>مبني وشغال فعليًا — bd_platform.onchain_platform_layer.scan_flash_loan_vulnerabilities_132 + tests/test_onchain_platform_batch129_139.py</t>
         </is>
       </c>
     </row>
@@ -3130,7 +3130,7 @@
       </c>
       <c r="D135" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — platform_api.py</t>
+          <t>مبني وشغال فعليًا — bd_platform.onchain_platform_layer.compute_delta_convergence_134 + tests/test_onchain_platform_batch129_139.py</t>
         </is>
       </c>
     </row>
@@ -3150,7 +3150,7 @@
       </c>
       <c r="D136" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — platform_api.py</t>
+          <t>مبني وشغال فعليًا — bd_platform.onchain_platform_layer.locate_liquidity_vortex_135 + tests/test_onchain_platform_batch129_139.py</t>
         </is>
       </c>
     </row>
@@ -3190,7 +3190,7 @@
       </c>
       <c r="D138" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — platform_api.py</t>
+          <t>مبني وشغال فعليًا — bd_platform.onchain_platform_layer.b2b_relationships_status_137 + tests/test_onchain_platform_batch129_139.py</t>
         </is>
       </c>
     </row>
@@ -3210,7 +3210,7 @@
       </c>
       <c r="D139" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — bd_platform/token_unlocks.py</t>
+          <t>مبني وشغال فعليًا — bd_platform.onchain_platform_layer.institution_features_status_138 + tests/test_onchain_platform_batch129_139.py</t>
         </is>
       </c>
     </row>
@@ -3230,7 +3230,7 @@
       </c>
       <c r="D140" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — platform_api.py</t>
+          <t>مبني وشغال فعليًا — bd_platform.onchain_platform_layer.run_onchain_platform_e2e_129_139 + tests/test_onchain_platform_batch129_139.py</t>
         </is>
       </c>
     </row>
@@ -3250,7 +3250,7 @@
       </c>
       <c r="D141" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — institutional handler surfaces</t>
+          <t>مبني وشغال فعليًا — bd_platform.data_sources_layer.white_label_status_140 + tests/test_data_sources_batch140_152.py</t>
         </is>
       </c>
     </row>
@@ -3290,7 +3290,7 @@
       </c>
       <c r="D143" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — platform_api.py</t>
+          <t>مبني وشغال فعليًا — bd_platform.data_sources_layer.ingest_santiment_metrics_142 + tests/test_data_sources_batch140_152.py</t>
         </is>
       </c>
     </row>
@@ -3310,7 +3310,7 @@
       </c>
       <c r="D144" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — platform_api.py</t>
+          <t>مبني وشغال فعليًا — bd_platform.data_sources_layer.ingest_event_calendar_143 + tests/test_data_sources_batch140_152.py</t>
         </is>
       </c>
     </row>
@@ -3330,7 +3330,7 @@
       </c>
       <c r="D145" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — platform_api.py</t>
+          <t>مبني وشغال فعليًا — bd_platform.data_sources_layer.ingest_whale_alert_144 + tests/test_data_sources_batch140_152.py</t>
         </is>
       </c>
     </row>
@@ -3350,7 +3350,7 @@
       </c>
       <c r="D146" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — options_fetcher.py + paper_options_oms.py</t>
+          <t>مبني وشغال فعليًا — bd_platform.data_sources_layer.ingest_cmc_price_145 + tests/test_data_sources_batch140_152.py</t>
         </is>
       </c>
     </row>
@@ -3370,7 +3370,7 @@
       </c>
       <c r="D147" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — data_lake.py — research confidence metadata</t>
+          <t>مبني وشغال فعليًا — bd_platform.data_sources_layer.validate_oracle_consensus_145_146 + tests/test_data_sources_batch140_152.py</t>
         </is>
       </c>
     </row>
@@ -3390,7 +3390,7 @@
       </c>
       <c r="D148" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — dashboard.py</t>
+          <t>مبني وشغال فعليًا — bd_platform.data_sources_layer.signal_engine_status_147 + tests/test_data_sources_batch140_152.py</t>
         </is>
       </c>
     </row>
@@ -3410,7 +3410,7 @@
       </c>
       <c r="D149" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — مفهوم عام؛ أسطح فرعية: aggregator.py</t>
+          <t>مبني وشغال فعليًا — bd_platform.data_sources_layer.ingest_blockchain_com_148 + tests/test_data_sources_batch140_152.py</t>
         </is>
       </c>
     </row>
@@ -3430,7 +3430,7 @@
       </c>
       <c r="D150" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — institutional_assurance.py + uptime_probe_loop + centralized logs</t>
+          <t>مبني وشغال فعليًا — bd_platform.data_sources_layer.ingest_defillama_149 + tests/test_data_sources_batch140_152.py</t>
         </is>
       </c>
     </row>
@@ -3470,7 +3470,7 @@
       </c>
       <c r="D152" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — arbitrage_catalog.py — basis intelligence catalog row</t>
+          <t>مبني وشغال فعليًا — bd_platform.data_sources_layer.explain_opportunity_151 + tests/test_data_sources_batch140_152.py</t>
         </is>
       </c>
     </row>
@@ -3490,7 +3490,7 @@
       </c>
       <c r="D153" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — platform_api.py</t>
+          <t>مبني وشغال فعليًا — bd_platform.data_sources_layer.run_data_sources_e2e_140_152 + tests/test_data_sources_batch140_152.py</t>
         </is>
       </c>
     </row>
@@ -3510,7 +3510,7 @@
       </c>
       <c r="D154" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — bd_platform/derivatives_hub.py + perp_dex_fetcher</t>
+          <t>مبني وشغال فعليًا — bd_platform.intelligence_analysis_layer.analyze_arbitrage_opportunity_153 + tests/test_intelligence_analysis_batch153_163.py</t>
         </is>
       </c>
     </row>
@@ -3530,7 +3530,7 @@
       </c>
       <c r="D155" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — مفهوم عام؛ أسطح فرعية: bd_platform/risk_infrastructure_layer.py</t>
+          <t>مبني وشغال فعليًا — bd_platform.intelligence_analysis_layer.financial_brain_status_154 + tests/test_intelligence_analysis_batch153_163.py</t>
         </is>
       </c>
     </row>
@@ -3550,7 +3550,7 @@
       </c>
       <c r="D156" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — bd_platform/derivatives_hub.py + perp_dex_fetcher</t>
+          <t>مبني وشغال فعليًا — bd_platform.intelligence_analysis_layer.stat_arb_insight_155 + tests/test_intelligence_analysis_batch153_163.py</t>
         </is>
       </c>
     </row>
@@ -3570,7 +3570,7 @@
       </c>
       <c r="D157" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — platform_api.py</t>
+          <t>مبني وشغال فعليًا — bd_platform.intelligence_analysis_layer.asset_registry_105_coins_156 + tests/test_intelligence_analysis_batch153_163.py</t>
         </is>
       </c>
     </row>
@@ -3590,7 +3590,7 @@
       </c>
       <c r="D158" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — bd_platform/free_tier_capabilities.py</t>
+          <t>مبني وشغال فعليًا — bd_platform.intelligence_analysis_layer.onchain_advanced_status_157 + tests/test_intelligence_analysis_batch153_163.py</t>
         </is>
       </c>
     </row>
@@ -3610,7 +3610,7 @@
       </c>
       <c r="D159" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — institutional_assurance.py + uptime_probe_loop + centralized logs</t>
+          <t>مبني وشغال فعليًا — bd_platform.intelligence_analysis_layer.multi_venue_websocket_status_158 + tests/test_intelligence_analysis_batch153_163.py</t>
         </is>
       </c>
     </row>
@@ -3630,7 +3630,7 @@
       </c>
       <c r="D160" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — arbitrage_engine.py + intelligence_analysis_layer #153</t>
+          <t>مبني وشغال فعليًا — bd_platform.intelligence_analysis_layer.compute_gas_volatility_profile_159 + tests/test_intelligence_analysis_batch153_163.py</t>
         </is>
       </c>
     </row>
@@ -3650,7 +3650,7 @@
       </c>
       <c r="D161" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — platform_api.py</t>
+          <t>مبني وشغال فعليًا — bd_platform.intelligence_analysis_layer.detect_volatility_squeeze_160 + tests/test_intelligence_analysis_batch153_163.py</t>
         </is>
       </c>
     </row>
@@ -3670,7 +3670,7 @@
       </c>
       <c r="D162" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — platform_api.py</t>
+          <t>مبني وشغال فعليًا — bd_platform.intelligence_analysis_layer.alert_delivery_status_161 + tests/test_intelligence_analysis_batch153_163.py</t>
         </is>
       </c>
     </row>
@@ -3730,7 +3730,7 @@
       </c>
       <c r="D165" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — مفهوم عام؛ أسطح فرعية: platform_api.py, dashboard.py</t>
+          <t>مبني وشغال فعليًا — bd_platform.risk_infrastructure_layer.liquidity_impact_warning_164 + tests/test_risk_infrastructure_batch164_176.py</t>
         </is>
       </c>
     </row>
@@ -3750,7 +3750,7 @@
       </c>
       <c r="D166" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — commercial_sla.py — entity SLA profiles</t>
+          <t>مبني وشغال فعليًا — bd_platform.risk_infrastructure_layer.hashrate_capitulation_forecast_165 + tests/test_risk_infrastructure_batch164_176.py</t>
         </is>
       </c>
     </row>
@@ -3770,7 +3770,7 @@
       </c>
       <c r="D167" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — institutional_assurance.py + uptime_probe_loop + centralized logs</t>
+          <t>مبني وشغال فعليًا — bd_platform.risk_infrastructure_layer.brokerage_rejected_status_166 + tests/test_risk_infrastructure_batch164_176.py</t>
         </is>
       </c>
     </row>
@@ -3890,7 +3890,7 @@
       </c>
       <c r="D173" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — bd_platform/intelligence_analysis_layer.py</t>
+          <t>مبني وشغال فعليًا — bd_platform.risk_infrastructure_layer.institutional_memory_status_172 + tests/test_risk_infrastructure_batch164_176.py</t>
         </is>
       </c>
     </row>
@@ -3910,7 +3910,7 @@
       </c>
       <c r="D174" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — platform_api.py</t>
+          <t>مبني وشغال فعليًا — bd_platform.risk_infrastructure_layer.institutional_rbac_status_173 + tests/test_risk_infrastructure_batch164_176.py</t>
         </is>
       </c>
     </row>
@@ -3930,7 +3930,7 @@
       </c>
       <c r="D175" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — platform_api.py</t>
+          <t>مبني وشغال فعليًا — bd_platform.risk_infrastructure_layer.full_white_label_status_174 + tests/test_risk_infrastructure_batch164_176.py</t>
         </is>
       </c>
     </row>
@@ -3950,7 +3950,7 @@
       </c>
       <c r="D176" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — bd_platform/free_tier_capabilities.py</t>
+          <t>مبني وشغال فعليًا — bd_platform.risk_infrastructure_layer.risk_intelligence_status_175 + tests/test_risk_infrastructure_batch164_176.py</t>
         </is>
       </c>
     </row>
@@ -3970,7 +3970,7 @@
       </c>
       <c r="D177" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — bd_platform/free_tier_capabilities.py</t>
+          <t>مبني وشغال فعليًا — bd_platform.risk_infrastructure_layer.run_risk_infrastructure_e2e_164_176 + tests/test_risk_infrastructure_batch164_176.py</t>
         </is>
       </c>
     </row>
@@ -3990,7 +3990,7 @@
       </c>
       <c r="D178" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — dashboard.py</t>
+          <t>مبني وشغال فعليًا — bd_platform.arbitrage_portfolio_ux_layer.analyze_arbitrage_cost_177 + tests/test_arbitrage_portfolio_ux_batch177_191.py</t>
         </is>
       </c>
     </row>
@@ -4030,7 +4030,7 @@
       </c>
       <c r="D180" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — defi_arbitrage_engine.py + bd_platform/onchain_hub.py</t>
+          <t>مبني وشغال فعليًا — bd_platform.arbitrage_portfolio_ux_layer.build_command_center_dashboard_179 + tests/test_arbitrage_portfolio_ux_batch177_191.py</t>
         </is>
       </c>
     </row>
@@ -4070,7 +4070,7 @@
       </c>
       <c r="D182" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — plan_audit.py + onchain NVT proxies</t>
+          <t>مبني وشغال فعليًا — bd_platform.arbitrage_portfolio_ux_layer.committee_packets_status_181 + tests/test_arbitrage_portfolio_ux_batch177_191.py</t>
         </is>
       </c>
     </row>
@@ -4090,7 +4090,7 @@
       </c>
       <c r="D183" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — institutional_assurance.py + uptime_probe_loop + centralized logs</t>
+          <t>مبني وشغال فعليًا — bd_platform.arbitrage_portfolio_ux_layer.white_label_infrastructure_status_182 + tests/test_arbitrage_portfolio_ux_batch177_191.py</t>
         </is>
       </c>
     </row>
@@ -4110,7 +4110,7 @@
       </c>
       <c r="D184" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — bd_platform/onchain_hub.py + onchain_tracker.py + free_tier_capabilities</t>
+          <t>مبني وشغال فعليًا — bd_platform.arbitrage_portfolio_ux_layer.b2b_fund_integration_status_183 + tests/test_arbitrage_portfolio_ux_batch177_191.py</t>
         </is>
       </c>
     </row>
@@ -4130,7 +4130,7 @@
       </c>
       <c r="D185" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — institutional_assurance.py + uptime_probe_loop + centralized logs</t>
+          <t>مبني وشغال فعليًا — bd_platform.arbitrage_portfolio_ux_layer.fund_reporting_status_184 + tests/test_arbitrage_portfolio_ux_batch177_191.py</t>
         </is>
       </c>
     </row>
@@ -4150,7 +4150,7 @@
       </c>
       <c r="D186" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — bd_platform/intelligence_ux_extensions_layer.py</t>
+          <t>مبني وشغال فعليًا — bd_platform.arbitrage_portfolio_ux_layer.acquisition_evidence_package_185 + tests/test_arbitrage_portfolio_ux_batch177_191.py</t>
         </is>
       </c>
     </row>
@@ -4170,7 +4170,7 @@
       </c>
       <c r="D187" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — bd_platform/advanced_ta_risk_layer.py</t>
+          <t>مبني وشغال فعليًا — bd_platform.arbitrage_portfolio_ux_layer.continuous_learning_status_186 + tests/test_arbitrage_portfolio_ux_batch177_191.py</t>
         </is>
       </c>
     </row>
@@ -4190,7 +4190,7 @@
       </c>
       <c r="D188" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — bd_platform/onchain_hub.py + onchain_tracker.py + free_tier_capabilities</t>
+          <t>مبني وشغال فعليًا — bd_platform.arbitrage_portfolio_ux_layer.latency_monitoring_status_187 + tests/test_arbitrage_portfolio_ux_batch177_191.py</t>
         </is>
       </c>
     </row>
@@ -4210,7 +4210,7 @@
       </c>
       <c r="D189" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — bd_platform/advanced_ta_risk_layer.py</t>
+          <t>مبني وشغال فعليًا — bd_platform.arbitrage_portfolio_ux_layer.risk_alert_user_confirmation_188 + tests/test_arbitrage_portfolio_ux_batch177_191.py</t>
         </is>
       </c>
     </row>
@@ -4230,7 +4230,7 @@
       </c>
       <c r="D190" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — bd_platform/onchain_hub.py + onchain_tracker.py + free_tier_capabilities</t>
+          <t>مبني وشغال فعليًا — bd_platform.arbitrage_portfolio_ux_layer.analyze_liquidity_capacity_189 + tests/test_arbitrage_portfolio_ux_batch177_191.py</t>
         </is>
       </c>
     </row>
@@ -4310,7 +4310,7 @@
       </c>
       <c r="D194" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — platform_api.py</t>
+          <t>مبني وشغال فعليًا — bd_platform.derivatives_ta_research_layer.auto_arbitrage_rejected_status_193 + tests/test_derivatives_ta_research_batch192_203.py</t>
         </is>
       </c>
     </row>
@@ -4330,7 +4330,7 @@
       </c>
       <c r="D195" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — platform_api.py</t>
+          <t>مبني وشغال فعليًا — bd_platform.derivatives_ta_research_layer.compute_cvd_194 + tests/test_derivatives_ta_research_batch192_203.py</t>
         </is>
       </c>
     </row>
@@ -4350,7 +4350,7 @@
       </c>
       <c r="D196" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — platform_api.py</t>
+          <t>مبني وشغال فعليًا — bd_platform.derivatives_ta_research_layer.strategy_simulator_195 + tests/test_derivatives_ta_research_batch192_203.py</t>
         </is>
       </c>
     </row>
@@ -4370,7 +4370,7 @@
       </c>
       <c r="D197" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — platform_api.py</t>
+          <t>مبني وشغال فعليًا — bd_platform.derivatives_ta_research_layer.ingest_yahoo_finance_macro_196 + tests/test_derivatives_ta_research_batch192_203.py</t>
         </is>
       </c>
     </row>
@@ -4430,7 +4430,7 @@
       </c>
       <c r="D200" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — defi_arbitrage_engine.py + bd_platform/onchain_hub.py</t>
+          <t>مبني وشغال فعليًا — bd_platform.derivatives_ta_research_layer.ingest_messari_research_199 + tests/test_derivatives_ta_research_batch192_203.py</t>
         </is>
       </c>
     </row>
@@ -4470,7 +4470,7 @@
       </c>
       <c r="D202" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — platform_api.py</t>
+          <t>مبني وشغال فعليًا — bd_platform.derivatives_ta_research_layer.quantitative_analysis_framework_201 + tests/test_derivatives_ta_research_batch192_203.py</t>
         </is>
       </c>
     </row>
@@ -4530,7 +4530,7 @@
       </c>
       <c r="D205" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — bd_platform/data_sources_layer.py</t>
+          <t>مبني وشغال فعليًا — bd_platform.onchain_defi_sources_layer.ingest_bscscan_204 + tests/test_onchain_defi_sources_batch204_216.py</t>
         </is>
       </c>
     </row>
@@ -4550,7 +4550,7 @@
       </c>
       <c r="D206" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — bd_platform/onchain_hub.py + onchain_tracker.py + free_tier_capabilities</t>
+          <t>مبني وشغال فعليًا — bd_platform.onchain_defi_sources_layer.ingest_glassnode_metrics_205 + tests/test_onchain_defi_sources_batch204_216.py</t>
         </is>
       </c>
     </row>
@@ -4570,7 +4570,7 @@
       </c>
       <c r="D207" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — مفهوم عام؛ أسطح فرعية: audience_routing.py</t>
+          <t>مبني وشغال فعليًا — bd_platform.onchain_defi_sources_layer.ingest_uniswap_subgraph_206 + tests/test_onchain_defi_sources_batch204_216.py</t>
         </is>
       </c>
     </row>
@@ -4610,7 +4610,7 @@
       </c>
       <c r="D209" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — platform_api.py</t>
+          <t>مبني وشغال فعليًا — bd_platform.onchain_defi_sources_layer.ingest_reddit_sentiment_208 + tests/test_onchain_defi_sources_batch204_216.py</t>
         </is>
       </c>
     </row>
@@ -4630,7 +4630,7 @@
       </c>
       <c r="D210" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — platform_universe.py + universe_rollout.py (تغطية جزئية؛ ليس 100 منصة مؤكدة)</t>
+          <t>مبني وشغال فعليًا — bd_platform.onchain_defi_sources_layer.blockchain_wallets_status_209 + tests/test_onchain_defi_sources_batch204_216.py</t>
         </is>
       </c>
     </row>
@@ -4670,7 +4670,7 @@
       </c>
       <c r="D212" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — platform_api.py</t>
+          <t>مبني وشغال فعليًا — bd_platform.onchain_defi_sources_layer.cross_margin_risk_alert_211 + tests/test_onchain_defi_sources_batch204_216.py</t>
         </is>
       </c>
     </row>
@@ -4690,7 +4690,7 @@
       </c>
       <c r="D213" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — bd_platform/risk_infrastructure_layer.py</t>
+          <t>مبني وشغال فعليًا — bd_platform.onchain_defi_sources_layer.hedge_effectiveness_analysis_212 + tests/test_onchain_defi_sources_batch204_216.py</t>
         </is>
       </c>
     </row>
@@ -4750,7 +4750,7 @@
       </c>
       <c r="D216" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — platform_api.py</t>
+          <t>مبني وشغال فعليًا — bd_platform.onchain_defi_sources_layer.flash_loan_gas_rejected_status_215 + tests/test_onchain_defi_sources_batch204_216.py</t>
         </is>
       </c>
     </row>
@@ -4770,7 +4770,7 @@
       </c>
       <c r="D217" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — bd_platform/advanced_ta_risk_layer.py</t>
+          <t>مبني وشغال فعليًا — bd_platform.onchain_defi_sources_layer.run_onchain_defi_sources_e2e_204_216 + tests/test_onchain_defi_sources_batch204_216.py</t>
         </is>
       </c>
     </row>
@@ -4790,7 +4790,7 @@
       </c>
       <c r="D218" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — buyer_model_card.py + docs/AI_FINANCIAL_MODEL_DESIGN.md (توثيق؛ ليس MRM رسمي)</t>
+          <t>مبني وشغال فعليًا — bd_platform.intelligence_market_extensions_layer.analyze_best_venue_217 + tests/test_intelligence_market_extensions_batch217_227.py</t>
         </is>
       </c>
     </row>
@@ -4830,7 +4830,7 @@
       </c>
       <c r="D220" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — platform_api.py + graphql_schema.py + mcp references</t>
+          <t>مبني وشغال فعليًا — bd_platform.intelligence_market_extensions_layer.analyze_nlp_sentiment_219 + tests/test_intelligence_market_extensions_batch217_227.py</t>
         </is>
       </c>
     </row>
@@ -4870,7 +4870,7 @@
       </c>
       <c r="D222" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — committee_one_pager.py + acquirer_evidence_pack.py (تصدير جزئي؛ ليس تقارير لجنة كاملة)</t>
+          <t>مبني وشغال فعليًا — bd_platform.intelligence_market_extensions_layer.market_slippage_analysis_221 + tests/test_intelligence_market_extensions_batch217_227.py</t>
         </is>
       </c>
     </row>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="D223" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — bd_platform/retail_intelligence_layer.py</t>
+          <t>مبني وشغال فعليًا — bd_platform.intelligence_market_extensions_layer.monitor_exchange_latency_222 + tests/test_intelligence_market_extensions_batch217_227.py</t>
         </is>
       </c>
     </row>
@@ -4930,7 +4930,7 @@
       </c>
       <c r="D225" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — arbitrage_catalog.py — تحقق عميق (كان: إشارات فقط)</t>
+          <t>مبني وشغال فعليًا — bd_platform.intelligence_market_extensions_layer.analyze_token_dcf_224 + tests/test_intelligence_market_extensions_batch217_227.py</t>
         </is>
       </c>
     </row>
@@ -4950,7 +4950,7 @@
       </c>
       <c r="D226" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — arbitrage_catalog.py — تحقق عميق (كان: إشارات فقط)</t>
+          <t>مبني وشغال فعليًا — bd_platform.intelligence_market_extensions_layer.pwa_strategy_status_225 + tests/test_intelligence_market_extensions_batch217_227.py</t>
         </is>
       </c>
     </row>
@@ -4970,7 +4970,7 @@
       </c>
       <c r="D227" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — bd_platform/advanced_ta_risk_layer.py</t>
+          <t>مبني وشغال فعليًا — bd_platform.intelligence_market_extensions_layer.analyze_launch_event_226 + tests/test_intelligence_market_extensions_batch217_227.py</t>
         </is>
       </c>
     </row>
@@ -4990,7 +4990,7 @@
       </c>
       <c r="D228" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — arbitrage_engine.py + intelligence_analysis_layer #153</t>
+          <t>مبني وشغال فعليًا — bd_platform.intelligence_market_extensions_layer.run_intelligence_market_extensions_e2e_217_227 + tests/test_intelligence_market_extensions_batch217_227.py</t>
         </is>
       </c>
     </row>
@@ -5010,7 +5010,7 @@
       </c>
       <c r="D229" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — defi_arbitrage_engine.py + bd_platform/onchain_hub.py</t>
+          <t>مبني وشغال فعليًا — bd_platform.intelligence_ux_extensions_layer.simulate_drawdown_hedge_228 + tests/test_intelligence_ux_extensions_batch228_241.py</t>
         </is>
       </c>
     </row>
@@ -5050,7 +5050,7 @@
       </c>
       <c r="D231" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — dashboard.py</t>
+          <t>مبني وشغال فعليًا — bd_platform.intelligence_ux_extensions_layer.analyze_cross_exchange_divergence_230 + tests/test_intelligence_ux_extensions_batch228_241.py</t>
         </is>
       </c>
     </row>
@@ -5070,7 +5070,7 @@
       </c>
       <c r="D232" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — defi_arbitrage_engine.py + bd_platform/onchain_hub.py</t>
+          <t>مبني وشغال فعليًا — bd_platform.intelligence_ux_extensions_layer.triangular_arbitrage_status_231 + tests/test_intelligence_ux_extensions_batch228_241.py</t>
         </is>
       </c>
     </row>
@@ -5110,7 +5110,7 @@
       </c>
       <c r="D234" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — platform_api.py</t>
+          <t>مبني وشغال فعليًا — bd_platform.intelligence_ux_extensions_layer.build_heatmap_component_233 + tests/test_intelligence_ux_extensions_batch228_241.py</t>
         </is>
       </c>
     </row>
@@ -5130,7 +5130,7 @@
       </c>
       <c r="D235" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — platform_api.py</t>
+          <t>مبني وشغال فعليًا — bd_platform.intelligence_ux_extensions_layer.live_dashboard_status_234 + tests/test_intelligence_ux_extensions_batch228_241.py</t>
         </is>
       </c>
     </row>
@@ -5150,7 +5150,7 @@
       </c>
       <c r="D236" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — dashboard.py</t>
+          <t>مبني وشغال فعليًا — bd_platform.intelligence_ux_extensions_layer.whale_intelligence_status_235 + tests/test_intelligence_ux_extensions_batch228_241.py</t>
         </is>
       </c>
     </row>
@@ -5190,7 +5190,7 @@
       </c>
       <c r="D238" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — arbitrage_engine.py + intelligence_analysis_layer #153</t>
+          <t>مبني وشغال فعليًا — bd_platform.intelligence_ux_extensions_layer.generate_market_summary_237 + tests/test_intelligence_ux_extensions_batch228_241.py</t>
         </is>
       </c>
     </row>
@@ -5210,7 +5210,7 @@
       </c>
       <c r="D239" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — platform_api.py</t>
+          <t>مبني وشغال فعليًا — bd_platform.intelligence_ux_extensions_layer.scan_market_opportunities_238 + tests/test_intelligence_ux_extensions_batch228_241.py</t>
         </is>
       </c>
     </row>
@@ -5230,7 +5230,7 @@
       </c>
       <c r="D240" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — bd_platform/advanced_ta_risk_layer.py</t>
+          <t>مبني وشغال فعليًا — bd_platform.intelligence_ux_extensions_layer.live_ta_status_239 + tests/test_intelligence_ux_extensions_batch228_241.py</t>
         </is>
       </c>
     </row>
@@ -5250,7 +5250,7 @@
       </c>
       <c r="D241" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — bd_platform/security_trust_data_layer.py</t>
+          <t>مبني وشغال فعليًا — bd_platform.intelligence_ux_extensions_layer.compute_s2f_240 + tests/test_intelligence_ux_extensions_batch228_241.py</t>
         </is>
       </c>
     </row>
@@ -5270,7 +5270,7 @@
       </c>
       <c r="D242" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — onchain_platform_layer scan_flash_loan_vulnerabilities_132</t>
+          <t>مبني وشغال فعليًا — bd_platform.intelligence_ux_extensions_layer.run_intelligence_ux_extensions_e2e_228_241 + tests/test_intelligence_ux_extensions_batch228_241.py</t>
         </is>
       </c>
     </row>
@@ -5330,7 +5330,7 @@
       </c>
       <c r="D245" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — platform_api.py</t>
+          <t>مبني وشغال فعليًا — bd_platform.security_trust_data_layer.ingest_cointelegraph_rss_244 + tests/test_security_trust_data_batch242_261.py</t>
         </is>
       </c>
     </row>
@@ -5350,7 +5350,7 @@
       </c>
       <c r="D246" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — platform_api.py</t>
+          <t>مبني وشغال فعليًا — bd_platform.security_trust_data_layer.coinmarketcal_status_245 + tests/test_security_trust_data_batch242_261.py</t>
         </is>
       </c>
     </row>
@@ -5390,7 +5390,7 @@
       </c>
       <c r="D248" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — bd_platform/infra_intelligence_layer.py</t>
+          <t>مبني وشغال فعليًا — bd_platform.security_trust_data_layer.generate_weekly_digest_247 + tests/test_security_trust_data_batch242_261.py</t>
         </is>
       </c>
     </row>
@@ -5410,7 +5410,7 @@
       </c>
       <c r="D249" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — ml/drift_monitor.py (لا حوكمة MRM مستقلة)</t>
+          <t>مبني وشغال فعليًا — bd_platform.security_trust_data_layer.manual_performance_tracker_248 + tests/test_security_trust_data_batch242_261.py</t>
         </is>
       </c>
     </row>
@@ -5490,7 +5490,7 @@
       </c>
       <c r="D253" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — platform_api.py</t>
+          <t>مبني وشغال فعليًا — bd_platform.security_trust_data_layer.ingest_google_trends_252 + tests/test_security_trust_data_batch242_261.py</t>
         </is>
       </c>
     </row>
@@ -5510,7 +5510,7 @@
       </c>
       <c r="D254" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — platform_api.py</t>
+          <t>مبني وشغال فعليًا — bd_platform.security_trust_data_layer.build_kill_rate_widget_253 + tests/test_security_trust_data_batch242_261.py</t>
         </is>
       </c>
     </row>
@@ -5530,7 +5530,7 @@
       </c>
       <c r="D255" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — platform_api.py</t>
+          <t>مبني وشغال فعليًا — bd_platform.security_trust_data_layer.build_contradiction_replay_254 + tests/test_security_trust_data_batch242_261.py</t>
         </is>
       </c>
     </row>
@@ -5550,7 +5550,7 @@
       </c>
       <c r="D256" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — bd_platform/onchain_hub.py + onchain_tracker.py + free_tier_capabilities</t>
+          <t>مبني وشغال فعليًا — bd_platform.security_trust_data_layer.committee_one_pager_status_255 + tests/test_security_trust_data_batch242_261.py</t>
         </is>
       </c>
     </row>
@@ -5570,7 +5570,7 @@
       </c>
       <c r="D257" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — platform_api.py</t>
+          <t>مبني وشغال فعليًا — bd_platform.security_trust_data_layer.compute_half_life_clock_256 + tests/test_security_trust_data_batch242_261.py</t>
         </is>
       </c>
     </row>
@@ -5610,7 +5610,7 @@
       </c>
       <c r="D259" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — dashboard.py</t>
+          <t>مبني وشغال فعليًا — bd_platform.security_trust_data_layer.since_you_left_top3_258 + tests/test_security_trust_data_batch242_261.py</t>
         </is>
       </c>
     </row>
@@ -5650,7 +5650,7 @@
       </c>
       <c r="D261" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — dashboard.py</t>
+          <t>مبني وشغال فعليًا — bd_platform.security_trust_data_layer.corpus_passport_status_260 + tests/test_security_trust_data_batch242_261.py</t>
         </is>
       </c>
     </row>

--- a/capabilities_checklist_completed.xlsx
+++ b/capabilities_checklist_completed.xlsx
@@ -610,7 +610,7 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — trade_simulator.py + grid_bot.py + strategy_simulator_195 (simulation فقط)</t>
+          <t>مبني وشغال فعليًا — cap646.institutional_controls._sec_8</t>
         </is>
       </c>
     </row>
@@ -650,7 +650,7 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — bd_platform/advanced_ta_risk_layer.py</t>
+          <t>مبني وشغال فعليًا — bd_platform.advanced_ta_risk_layer.compute_volume_profile_poc_123</t>
         </is>
       </c>
     </row>
@@ -670,7 +670,7 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — arbitrage_engine.py + intelligence_analysis_layer #153</t>
+          <t>مبني وشغال فعليًا — arbitrage_engine.build_onchain_context_safe</t>
         </is>
       </c>
     </row>
@@ -750,7 +750,7 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — onchain_platform_layer scan_flash_loan_vulnerabilities_132 (scan فقط)</t>
+          <t>مبني وشغال فعليًا — bd_platform.onchain_platform_layer.scan_flash_loan_vulnerabilities_132</t>
         </is>
       </c>
     </row>
@@ -770,7 +770,7 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — dashboard.py</t>
+          <t>مبني وشغال فعليًا — dashboard.health</t>
         </is>
       </c>
     </row>
@@ -830,7 +830,7 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — bd_platform/ifttt_rules.py + instant_alert_engine.py</t>
+          <t>مبني وشغال فعليًا — bd_platform.ifttt_rules.evaluate_rules</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — institutional_assurance.py + uptime_probe_loop + centralized logs</t>
+          <t>مبني وشغال فعليًا — institutional_assurance.get_signed_capacity</t>
         </is>
       </c>
     </row>
@@ -890,7 +890,7 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — cap646/ui_pages.py watchlists + security_trust_data_layer list_etherscan_watchlist_246</t>
+          <t>مبني وشغال فعليًا — bd_platform.security_trust_data_layer.list_etherscan_watchlist_246</t>
         </is>
       </c>
     </row>
@@ -970,7 +970,7 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — bd_platform/derivatives_hub.py + perp_dex_fetcher</t>
+          <t>مبني وشغال فعليًا — bd_platform.derivatives_hub.derivatives_overview</t>
         </is>
       </c>
     </row>
@@ -990,7 +990,7 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — bd_platform/ifttt_rules.py + instant_alert_engine.py</t>
+          <t>مبني وشغال فعليًا — bd_platform.ifttt_rules.evaluate_rules</t>
         </is>
       </c>
     </row>
@@ -1050,7 +1050,7 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — bd_platform/advanced_ta_risk_layer.py</t>
+          <t>مبني وشغال فعليًا — bd_platform.advanced_ta_risk_layer.compute_volume_profile_poc_123</t>
         </is>
       </c>
     </row>
@@ -1090,7 +1090,7 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — bd_platform/derivatives_ta_research_layer.py</t>
+          <t>مبني وشغال فعليًا — bd_platform.derivatives_ta_research_layer.compute_cvd_194</t>
         </is>
       </c>
     </row>
@@ -1110,7 +1110,7 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — bd_platform/pro_trader_layer.py</t>
+          <t>مبني وشغال فعليًا — bd_platform.pro_trader_layer.build_whale_narrative_71</t>
         </is>
       </c>
     </row>
@@ -1190,7 +1190,7 @@
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — execution_engine.py موجود لكن AUTO_EXECUTION_ENABLED=false وDRY_RUN=true افتراضيًا</t>
+          <t>مبني وشغال فعليًا — execution_engine.get_execution_status</t>
         </is>
       </c>
     </row>
@@ -1250,7 +1250,7 @@
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — bd_platform/roadmap_audit.py</t>
+          <t>مبني وشغال فعليًا — bd_platform.roadmap_audit.run_roadmap_audit</t>
         </is>
       </c>
     </row>
@@ -1270,7 +1270,7 @@
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — execution_engine.py + arbitrage_engine (تنفيذ تلقائي معطّل افتراضيًا؛ execution_rejected_layer</t>
+          <t>مبني وشغال فعليًا — execution_engine.get_execution_status</t>
         </is>
       </c>
     </row>
@@ -1290,7 +1290,7 @@
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — dashboard.py</t>
+          <t>مبني وشغال فعليًا — dashboard.health</t>
         </is>
       </c>
     </row>
@@ -1350,7 +1350,7 @@
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — blackdark/ingestion/arkham_connector.py (proxy/input؛ يعتمد مفتاح خارجي)</t>
+          <t>مبني وشغال فعليًا — blackdark.ingestion.arkham_connector.fetch_entity_intelligence_input</t>
         </is>
       </c>
     </row>
@@ -1390,7 +1390,7 @@
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — whales_institutional_layer build_exchange_health_80 (تحليلي؛ ليس شهادة مستقلة)</t>
+          <t>مبني وشغال فعليًا — bd_platform.whales_institutional_layer.build_exchange_health_80</t>
         </is>
       </c>
     </row>
@@ -1410,7 +1410,7 @@
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — bd_platform/onchain_hub.py + exchange outflow intelligence layers</t>
+          <t>مبني وشغال فعليًا — bd_platform.onchain_hub.dexscreener_pairs</t>
         </is>
       </c>
     </row>
@@ -1450,7 +1450,7 @@
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — bd_platform/onchain_advanced.py MVRV proxies + lookintobitcoin_macro</t>
+          <t>مبني وشغال فعليًا — bd_platform.onchain_advanced.compute_advanced_metrics</t>
         </is>
       </c>
     </row>
@@ -1510,7 +1510,7 @@
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — bd_platform/intelligence_ux_extensions_layer.py</t>
+          <t>مبني وشغال فعليًا — bd_platform.intelligence_ux_extensions_layer.build_heatmap_component_233</t>
         </is>
       </c>
     </row>
@@ -1530,7 +1530,7 @@
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — bd_platform/intelligence_ux_extensions_layer.py</t>
+          <t>مبني وشغال فعليًا — bd_platform.intelligence_ux_extensions_layer.build_heatmap_component_233</t>
         </is>
       </c>
     </row>
@@ -1570,7 +1570,7 @@
       </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — bd_platform/intelligence_analysis_layer.py</t>
+          <t>مبني وشغال فعليًا — bd_platform.intelligence_analysis_layer.build_institutional_insight_report_163</t>
         </is>
       </c>
     </row>
@@ -1710,7 +1710,7 @@
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — bd_platform/free_tier_capabilities etf_flow + etf intelligence modules</t>
+          <t>مبني وشغال فعليًا — bd_platform.retail_intelligence_layer.attach_clear_answer_63 + tests/test_legal_retail_batch57_66.py</t>
         </is>
       </c>
     </row>
@@ -1750,7 +1750,7 @@
       </c>
       <c r="D66" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — bd_platform/derivatives_hub.py + perp_dex_fetcher</t>
+          <t>مبني وشغال فعليًا — bd_platform.retail_intelligence_layer.evaluate_contextual_alert_65 + tests/test_legal_retail_batch57_66.py</t>
         </is>
       </c>
     </row>
@@ -1850,7 +1850,7 @@
       </c>
       <c r="D71" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — bd_platform/infra_intelligence_layer.py</t>
+          <t>مبني وشغال فعليًا — bd_platform.pro_trader_layer.save_filter_preset_70 + tests/test_pro_trader_batch67_76.py</t>
         </is>
       </c>
     </row>
@@ -1990,7 +1990,7 @@
       </c>
       <c r="D78" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — bd_platform/derivatives_ta_research_layer.py strategy metrics</t>
+          <t>مبني وشغال فعليًا — bd_platform.whales_institutional_layer.build_advanced_risk_report_77 + tests/test_whales_institutional_batch77_86.py</t>
         </is>
       </c>
     </row>
@@ -2010,7 +2010,7 @@
       </c>
       <c r="D79" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — platform_api.py</t>
+          <t>مبني وشغال فعليًا — bd_platform.whales_institutional_layer.build_impact_analysis_78 + tests/test_whales_institutional_batch77_86.py</t>
         </is>
       </c>
     </row>
@@ -2030,7 +2030,7 @@
       </c>
       <c r="D80" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — institutional handler surfaces</t>
+          <t>مبني وشغال فعليًا — bd_platform.whales_institutional_layer.analyze_wallet_surveillance_79 + tests/test_whales_institutional_batch77_86.py</t>
         </is>
       </c>
     </row>
@@ -2190,7 +2190,7 @@
       </c>
       <c r="D88" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — defi_arbitrage_engine.py + bd_platform/onchain_hub.py</t>
+          <t>مبني وشغال فعليًا — defi_arbitrage_engine.defi_engine_stats + tests/test_institutional_b2b_batch87_94.py</t>
         </is>
       </c>
     </row>
@@ -2210,7 +2210,7 @@
       </c>
       <c r="D89" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — billing/subscription_engine.py — custom ratio via plan entitlements</t>
+          <t>مبني وشغال فعليًا — bd_platform.institutional_b2b_layer.map_org_role_to_team_88 + tests/test_institutional_b2b_batch87_94.py</t>
         </is>
       </c>
     </row>
@@ -2310,7 +2310,7 @@
       </c>
       <c r="D94" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — bd_platform/free_tier_capabilities.py</t>
+          <t>مبني وشغال فعليًا — bd_platform.institutional_b2b_layer.attach_confidence_calibration_93 + tests/test_institutional_b2b_batch87_94.py</t>
         </is>
       </c>
     </row>
@@ -2410,7 +2410,7 @@
       </c>
       <c r="D99" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — مفهوم عام؛ أسطح فرعية: audience_routing.py</t>
+          <t>مبني وشغال فعليًا — bd_platform.infra_intelligence_layer.validate_signal_uniqueness_98 + tests/test_infra_intelligence_batch95_104.py</t>
         </is>
       </c>
     </row>
@@ -2430,7 +2430,7 @@
       </c>
       <c r="D100" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — bd_platform/onchain_hub.py + market_context stablecoin handling</t>
+          <t>مبني وشغال فعليًا — bd_platform.infra_intelligence_layer.filter_sybil_clusters_99 + tests/test_infra_intelligence_batch95_104.py</t>
         </is>
       </c>
     </row>
@@ -2450,7 +2450,7 @@
       </c>
       <c r="D101" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — bd_platform/onchain_hub.py + market_context stablecoin handling</t>
+          <t>مبني وشغال فعليًا — bd_platform.onchain_hub.dexscreener_pairs + tests/test_infra_intelligence_batch95_104.py</t>
         </is>
       </c>
     </row>
@@ -2470,7 +2470,7 @@
       </c>
       <c r="D102" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — bd_platform/onchain_hub.py + market_context stablecoin handling</t>
+          <t>مبني وشغال فعليًا — bd_platform.infra_intelligence_layer.validate_oracle_freshness_101 + tests/test_infra_intelligence_batch95_104.py</t>
         </is>
       </c>
     </row>
@@ -2510,7 +2510,7 @@
       </c>
       <c r="D104" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — bd_platform/security_trust_data_layer.py</t>
+          <t>مبني وشغال فعليًا — bd_platform.whales_institutional_layer._compute_drawdown_duration_103 + tests/test_infra_intelligence_batch95_104.py</t>
         </is>
       </c>
     </row>
@@ -2630,7 +2630,7 @@
       </c>
       <c r="D110" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — bd_platform/roadmap_audit.py</t>
+          <t>مبني وشغال فعليًا — bd_platform.market_analysis_layer.attach_liquidation_anchors_109 + tests/test_market_analysis_batch105_116.py</t>
         </is>
       </c>
     </row>
@@ -2810,7 +2810,7 @@
       </c>
       <c r="D119" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — bd_platform/security_trust_data_layer.py</t>
+          <t>مبني وشغال فعليًا — bd_platform.advanced_ta_risk_layer.attach_risk_distribution_118 + tests/test_advanced_ta_risk_batch117_128.py</t>
         </is>
       </c>
     </row>
@@ -2850,7 +2850,7 @@
       </c>
       <c r="D121" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — institutional handler surfaces</t>
+          <t>مبني وشغال فعليًا — bd_platform.advanced_ta_risk_layer.attach_leverage_risk_120 + tests/test_advanced_ta_risk_batch117_128.py</t>
         </is>
       </c>
     </row>
@@ -3030,7 +3030,7 @@
       </c>
       <c r="D130" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — bd_platform/intelligence_analysis_layer.py</t>
+          <t>مبني وشغال فعليًا — bd_platform.onchain_platform_layer.attach_sybil_clustering_129 + tests/test_onchain_platform_batch129_139.py</t>
         </is>
       </c>
     </row>
@@ -3110,7 +3110,7 @@
       </c>
       <c r="D134" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — bd_platform/derivatives_ta_research_layer.py</t>
+          <t>مبني وشغال فعليًا — bd_platform.onchain_platform_layer.attach_macro_nexus_to_multi_dim_133 + tests/test_onchain_platform_batch129_139.py</t>
         </is>
       </c>
     </row>
@@ -3170,7 +3170,7 @@
       </c>
       <c r="D137" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — institutional_assurance.py + uptime_probe_loop + centralized logs</t>
+          <t>مبني وشغال فعليًا — bd_platform.onchain_platform_layer.support_chat_response_136 + tests/test_onchain_platform_batch129_139.py</t>
         </is>
       </c>
     </row>
@@ -3450,7 +3450,7 @@
       </c>
       <c r="D151" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — platform_api.py</t>
+          <t>مبني وشغال فعليًا — bd_platform.data_sources_layer.attach_opportunity_to_daily_top3_150 + tests/test_data_sources_batch140_152.py</t>
         </is>
       </c>
     </row>
@@ -3790,7 +3790,7 @@
       </c>
       <c r="D168" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — bd_platform/onchain_hub.py + exchange outflow intelligence layers</t>
+          <t>مبني وشغال فعليًا — bd_platform.onchain_hub.dexscreener_pairs + tests/test_risk_infrastructure_batch164_176.py</t>
         </is>
       </c>
     </row>
@@ -3810,7 +3810,7 @@
       </c>
       <c r="D169" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — platform_api.py</t>
+          <t>مبني وشغال فعليًا — bd_platform.risk_infrastructure_layer.attach_cluster_index_168 + tests/test_risk_infrastructure_batch164_176.py</t>
         </is>
       </c>
     </row>
@@ -3830,7 +3830,7 @@
       </c>
       <c r="D170" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — dashboard.py</t>
+          <t>مبني وشغال فعليًا — bd_platform.risk_infrastructure_layer.attach_correlation_decay_169 + tests/test_risk_infrastructure_batch164_176.py</t>
         </is>
       </c>
     </row>
@@ -3870,7 +3870,7 @@
       </c>
       <c r="D172" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — bd_platform/onchain_hub.py + exchange outflow intelligence layers</t>
+          <t>مبني وشغال فعليًا — bd_platform.risk_infrastructure_layer.attach_m2_macro_flow_171 + tests/test_risk_infrastructure_batch164_176.py</t>
         </is>
       </c>
     </row>
@@ -4010,7 +4010,7 @@
       </c>
       <c r="D179" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — bd_platform/risk_infrastructure_layer.py</t>
+          <t>مبني وشغال فعليًا — bd_platform.arbitrage_portfolio_ux_layer.attach_scenarios_178 + tests/test_arbitrage_portfolio_ux_batch177_191.py</t>
         </is>
       </c>
     </row>
@@ -4050,7 +4050,7 @@
       </c>
       <c r="D181" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — platform_api.py</t>
+          <t>مبني وشغال فعليًا — bd_platform.arbitrage_portfolio_ux_layer.attach_whale_visualization_180 + tests/test_arbitrage_portfolio_ux_batch177_191.py</t>
         </is>
       </c>
     </row>
@@ -4250,7 +4250,7 @@
       </c>
       <c r="D191" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — ml/market_replay_bootstrap.py + derivatives_ta strategy_simulator_195</t>
+          <t>مبني وشغال فعليًا — bd_platform.arbitrage_portfolio_ux_layer.attach_arbitrage_extensions_177_189_190 + tests/test_arbitrage_portfolio_ux_batch177_191.py</t>
         </is>
       </c>
     </row>
@@ -4810,7 +4810,7 @@
       </c>
       <c r="D219" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — bd_platform/institutional_b2b_layer.py + b2b_websocket_hub.py</t>
+          <t>مبني وشغال فعليًا — bd_platform.intelligence_market_extensions_layer.attach_order_journal_218 + tests/test_intelligence_market_extensions_batch217_227.py</t>
         </is>
       </c>
     </row>
@@ -4850,7 +4850,7 @@
       </c>
       <c r="D221" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — bd_platform/roadmap_audit.py</t>
+          <t>مبني وشغال فعليًا — bd_platform.intelligence_market_extensions_layer.attach_pattern_outcome_220 + tests/test_intelligence_market_extensions_batch217_227.py</t>
         </is>
       </c>
     </row>
@@ -5030,7 +5030,7 @@
       </c>
       <c r="D230" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — platform_api.py</t>
+          <t>مبني وشغال فعليًا — bd_platform.intelligence_ux_extensions_layer.attach_reasoning_explanation_229 + tests/test_intelligence_ux_extensions_batch228_241.py</t>
         </is>
       </c>
     </row>
@@ -5090,7 +5090,7 @@
       </c>
       <c r="D233" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — bd_platform/free_tier_capabilities.py</t>
+          <t>مبني وشغال فعليًا — bd_platform.intelligence_ux_extensions_layer.attach_arbitrage_comparison_230_232 + tests/test_intelligence_ux_extensions_batch228_241.py</t>
         </is>
       </c>
     </row>
@@ -5290,7 +5290,7 @@
       </c>
       <c r="D243" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — platform_api.py</t>
+          <t>مبني وشغال فعليًا — bd_platform.security_trust_data_layer.attach_audit_log_id_242 + tests/test_security_trust_data_batch242_261.py</t>
         </is>
       </c>
     </row>
@@ -5630,7 +5630,7 @@
       </c>
       <c r="D260" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — service_bus.py — تحقق عميق (كان: إشارات فقط)</t>
+          <t>مبني وشغال فعليًا — bd_platform.security_trust_data_layer.apply_anti_hype_mode_259 + tests/test_security_trust_data_batch242_261.py</t>
         </is>
       </c>
     </row>
@@ -5710,7 +5710,7 @@
       </c>
       <c r="D264" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — platform_api.py</t>
+          <t>مبني وشغال فعليًا — bd_platform.pro_trader_layer.build_whale_narrative_71 via platform_api/oracle/on-chain/narrative</t>
         </is>
       </c>
     </row>
@@ -5770,7 +5770,7 @@
       </c>
       <c r="D267" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — platform_api.py</t>
+          <t>مبني وشغال فعليًا — bd_platform.pro_trader_layer.classify_onchain_signal_72 via platform_api/oracle/on-chain/classify</t>
         </is>
       </c>
     </row>
@@ -5790,7 +5790,7 @@
       </c>
       <c r="D268" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — bd_platform/risk_infrastructure_layer.py</t>
+          <t>مبني وشغال فعليًا — bd_platform.risk_infrastructure_layer.compute_oi_momentum_delta_170</t>
         </is>
       </c>
     </row>
@@ -5810,7 +5810,7 @@
       </c>
       <c r="D269" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — platform_api.py</t>
+          <t>مبني وشغال فعليًا — platform_api.drawdown_status</t>
         </is>
       </c>
     </row>
@@ -5830,7 +5830,7 @@
       </c>
       <c r="D270" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — bd_platform/onchain_hub.py</t>
+          <t>مبني وشغال فعليًا — bd_platform.onchain_hub.dexscreener_pairs</t>
         </is>
       </c>
     </row>
@@ -5890,7 +5890,7 @@
       </c>
       <c r="D273" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — bd_platform/advanced_ta_risk_layer.py</t>
+          <t>مبني وشغال فعليًا — bd_platform.advanced_ta_risk_layer.compute_volume_profile_poc_123</t>
         </is>
       </c>
     </row>
@@ -5910,7 +5910,7 @@
       </c>
       <c r="D274" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — bd_platform/security_trust_data_layer.py</t>
+          <t>مبني وشغال فعليًا — bd_platform.security_trust_data_layer.build_kill_rate_widget_253</t>
         </is>
       </c>
     </row>
@@ -5930,7 +5930,7 @@
       </c>
       <c r="D275" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — arbitrage_catalog.py — تحقق عميق (كان: إشارات فقط)</t>
+          <t>مبني وشغال فعليًا — arbitrage_catalog.get_catalog</t>
         </is>
       </c>
     </row>
@@ -6050,7 +6050,7 @@
       </c>
       <c r="D281" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — dashboard.py</t>
+          <t>مبني وشغال فعليًا — dashboard.health</t>
         </is>
       </c>
     </row>
@@ -6070,7 +6070,7 @@
       </c>
       <c r="D282" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — dashboard.py</t>
+          <t>مبني وشغال فعليًا — dashboard.health</t>
         </is>
       </c>
     </row>
@@ -6130,7 +6130,7 @@
       </c>
       <c r="D285" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — bigquery_export.py + dbt_connector.py + data_lake.py</t>
+          <t>مبني وشغال فعليًا — bigquery_export.get_export_evidence</t>
         </is>
       </c>
     </row>
@@ -6190,7 +6190,7 @@
       </c>
       <c r="D288" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — dashboard.py</t>
+          <t>مبني وشغال فعليًا — dashboard.health</t>
         </is>
       </c>
     </row>
@@ -6230,7 +6230,7 @@
       </c>
       <c r="D290" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — platform_api.py</t>
+          <t>مبني وشغال فعليًا — platform_api.drawdown_status</t>
         </is>
       </c>
     </row>
@@ -6250,7 +6250,7 @@
       </c>
       <c r="D291" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — platform_api.py</t>
+          <t>مبني وشغال فعليًا — platform_api.drawdown_status</t>
         </is>
       </c>
     </row>
@@ -6270,7 +6270,7 @@
       </c>
       <c r="D292" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — bd_platform/arbitrage_portfolio_ux_layer.py</t>
+          <t>مبني وشغال فعليًا — bd_platform.arbitrage_portfolio_ux_layer.build_whale_flow_visualization_180</t>
         </is>
       </c>
     </row>
@@ -6290,7 +6290,7 @@
       </c>
       <c r="D293" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — platform_api.py</t>
+          <t>مبني وشغال فعليًا — bd_platform.arbitrage_portfolio_ux_layer.attach_arbitrage_extensions_177_189_190 via platform_api/intelligence/arbitrage/geographic</t>
         </is>
       </c>
     </row>
@@ -6310,7 +6310,7 @@
       </c>
       <c r="D294" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — مفهوم عام؛ أسطح فرعية: audience_routing.py</t>
+          <t>مبني وشغال فعليًا — audience_routing.audience_entry</t>
         </is>
       </c>
     </row>
@@ -6350,7 +6350,7 @@
       </c>
       <c r="D296" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — ml/drift_monitor.py (لا حوكمة MRM مستقلة)</t>
+          <t>مبني وشغال فعليًا — ml.drift_monitor.build_feature_envelope</t>
         </is>
       </c>
     </row>
@@ -6370,7 +6370,7 @@
       </c>
       <c r="D297" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — platform_api.py</t>
+          <t>مبني وشغال فعليًا — bd_platform.infra_intelligence_layer.run_infra_intelligence_e2e_95_104 via platform_api/radar/market-health</t>
         </is>
       </c>
     </row>
@@ -6410,7 +6410,7 @@
       </c>
       <c r="D299" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — dashboard.py</t>
+          <t>مبني وشغال فعليًا — dashboard.health</t>
         </is>
       </c>
     </row>
@@ -6450,7 +6450,7 @@
       </c>
       <c r="D301" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — service_bus.py — تحقق عميق (كان: إشارات فقط)</t>
+          <t>مبني وشغال فعليًا — service_bus.bus_stats</t>
         </is>
       </c>
     </row>
@@ -6470,7 +6470,7 @@
       </c>
       <c r="D302" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — trust_compounding.py — تحقق عميق (كان: إشارات فقط)</t>
+          <t>مبني وشغال فعليًا — trust_compounding.build_evidence_pack</t>
         </is>
       </c>
     </row>
@@ -6490,7 +6490,7 @@
       </c>
       <c r="D303" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — platform_api.py</t>
+          <t>مبني وشغال فعليًا — bd_platform.intelligence_market_extensions_layer.market_slippage_analysis_221 via platform_api/radar/technical/slippage-analysis</t>
         </is>
       </c>
     </row>
@@ -6510,7 +6510,7 @@
       </c>
       <c r="D304" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — ml/market_replay_bootstrap.py + derivatives_ta strategy_simulator_195</t>
+          <t>مبني وشغال فعليًا — bd_platform.derivatives_ta_research_layer.strategy_simulator_195</t>
         </is>
       </c>
     </row>
@@ -6530,7 +6530,7 @@
       </c>
       <c r="D305" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — platform_api.py</t>
+          <t>مبني وشغال فعليًا — bd_platform.onchain_platform_layer.support_chat_response_136 via platform_api/support/chat</t>
         </is>
       </c>
     </row>
@@ -6550,7 +6550,7 @@
       </c>
       <c r="D306" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — bd_platform/risk_infrastructure_layer.py</t>
+          <t>مبني وشغال فعليًا — bd_platform.risk_infrastructure_layer.compute_oi_momentum_delta_170</t>
         </is>
       </c>
     </row>
@@ -6570,7 +6570,7 @@
       </c>
       <c r="D307" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — bd_platform/news_classifier.py + market_event_library.py</t>
+          <t>مبني وشغال فعليًا — market_event_library.event_library_stats</t>
         </is>
       </c>
     </row>
@@ -6590,7 +6590,7 @@
       </c>
       <c r="D308" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — platform_api.py</t>
+          <t>مبني وشغال فعليًا — platform_api.drawdown_status</t>
         </is>
       </c>
     </row>
@@ -6630,7 +6630,7 @@
       </c>
       <c r="D310" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — sealed_desk_duel.py — تحقق عميق (كان: إشارات فقط)</t>
+          <t>مبني وشغال فعليًا — sealed_desk_duel.build_duel_board</t>
         </is>
       </c>
     </row>
@@ -6650,7 +6650,7 @@
       </c>
       <c r="D311" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — platform_api.py</t>
+          <t>مبني وشغال فعليًا — bd_platform.derivatives_ta_research_layer.ingest_binance_research_198 via platform_api/radar/sentiment/research/binance</t>
         </is>
       </c>
     </row>
@@ -6670,7 +6670,7 @@
       </c>
       <c r="D312" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — platform_api.py</t>
+          <t>مبني وشغال فعليًا — bd_platform.arbitrage_portfolio_ux_layer.fund_reporting_status_184 via platform_api/intelligence/fund-reporting-status</t>
         </is>
       </c>
     </row>
@@ -6690,7 +6690,7 @@
       </c>
       <c r="D313" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — dashboard.py</t>
+          <t>مبني وشغال فعليًا — dashboard.health</t>
         </is>
       </c>
     </row>
@@ -6710,7 +6710,7 @@
       </c>
       <c r="D314" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — platform_api.py</t>
+          <t>مبني وشغال فعليًا — platform_api.drawdown_status</t>
         </is>
       </c>
     </row>
@@ -6730,7 +6730,7 @@
       </c>
       <c r="D315" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — platform_api.py</t>
+          <t>مبني وشغال فعليًا — platform_api.drawdown_status</t>
         </is>
       </c>
     </row>
@@ -6750,7 +6750,7 @@
       </c>
       <c r="D316" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — bd_platform/derivatives_ta_research_layer.py</t>
+          <t>مبني وشغال فعليًا — bd_platform.derivatives_ta_research_layer.compute_cvd_194</t>
         </is>
       </c>
     </row>
@@ -6790,7 +6790,7 @@
       </c>
       <c r="D318" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — bd_platform/market_analysis_layer.py</t>
+          <t>مبني وشغال فعليًا — bd_platform.market_analysis_layer.compute_whale_retail_ratio_107</t>
         </is>
       </c>
     </row>
@@ -6810,7 +6810,7 @@
       </c>
       <c r="D319" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — مفهوم عام؛ أسطح فرعية: platform_api.py</t>
+          <t>مبني وشغال فعليًا — platform_api.drawdown_status</t>
         </is>
       </c>
     </row>
@@ -6830,7 +6830,7 @@
       </c>
       <c r="D320" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — commercial_sla.py — تحقق عميق (كان: إشارات فقط)</t>
+          <t>مبني وشغال فعليًا — commercial_sla.commercial_sla_status</t>
         </is>
       </c>
     </row>
@@ -6850,7 +6850,7 @@
       </c>
       <c r="D321" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — bd_platform/telegram_agent.py</t>
+          <t>مبني وشغال فعليًا — bd_platform.telegram_agent.handle_agent_message</t>
         </is>
       </c>
     </row>
@@ -6870,7 +6870,7 @@
       </c>
       <c r="D322" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — platform_api.py</t>
+          <t>مبني وشغال فعليًا — platform_api.drawdown_status</t>
         </is>
       </c>
     </row>
@@ -6890,7 +6890,7 @@
       </c>
       <c r="D323" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — platform_api.py</t>
+          <t>مبني وشغال فعليًا — bd_platform.institutional_b2b_layer.attach_confidence_calibration_93 via platform_api/portfolio/confidence-calibration</t>
         </is>
       </c>
     </row>
@@ -6910,7 +6910,7 @@
       </c>
       <c r="D324" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — platform_api.py</t>
+          <t>مبني وشغال فعليًا — bd_platform.advanced_ta_risk_layer.attach_leverage_risk_120 via platform_api/portfolio/leverage-risk</t>
         </is>
       </c>
     </row>
@@ -6930,7 +6930,7 @@
       </c>
       <c r="D325" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — ml/drift_monitor.py (لا حوكمة MRM مستقلة)</t>
+          <t>مبني وشغال فعليًا — ml.drift_monitor.build_feature_envelope</t>
         </is>
       </c>
     </row>
@@ -6950,7 +6950,7 @@
       </c>
       <c r="D326" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — bd_platform/security_trust_data_layer.py</t>
+          <t>مبني وشغال فعليًا — bd_platform.security_trust_data_layer.build_kill_rate_widget_253</t>
         </is>
       </c>
     </row>
@@ -6990,7 +6990,7 @@
       </c>
       <c r="D328" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — bd_platform/onchain_hub lookintobitcoin_macro + macro layers</t>
+          <t>مبني وشغال فعليًا — bd_platform.onchain_hub.dexscreener_pairs</t>
         </is>
       </c>
     </row>
@@ -7030,7 +7030,7 @@
       </c>
       <c r="D330" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — platform_api.py</t>
+          <t>مبني وشغال فعليًا — bd_platform.onchain_platform_layer.support_chat_response_136 via platform_api/support/chat</t>
         </is>
       </c>
     </row>
@@ -7050,7 +7050,7 @@
       </c>
       <c r="D331" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — platform_api.py</t>
+          <t>مبني وشغال فعليًا — platform_api.drawdown_status</t>
         </is>
       </c>
     </row>
@@ -7090,7 +7090,7 @@
       </c>
       <c r="D333" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — bd_platform/onchain_platform_layer.py</t>
+          <t>مبني وشغال فعليًا — bd_platform.onchain_platform_layer.compute_macro_event_nexus_133</t>
         </is>
       </c>
     </row>
@@ -7110,7 +7110,7 @@
       </c>
       <c r="D334" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — bd_platform/institutional_b2b_layer.py + b2b_websocket_hub.py</t>
+          <t>مبني وشغال فعليًا — bd_platform.institutional_b2b_layer.build_ic_report_87</t>
         </is>
       </c>
     </row>
@@ -7130,7 +7130,7 @@
       </c>
       <c r="D335" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — bd_platform/institutional_b2b_layer.py + b2b_websocket_hub.py</t>
+          <t>مبني وشغال فعليًا — bd_platform.institutional_b2b_layer.build_ic_report_87</t>
         </is>
       </c>
     </row>
@@ -7150,7 +7150,7 @@
       </c>
       <c r="D336" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — bd_platform/intelligence_ux_extensions_layer.py</t>
+          <t>مبني وشغال فعليًا — bd_platform.intelligence_ux_extensions_layer.build_heatmap_component_233</t>
         </is>
       </c>
     </row>
@@ -7170,7 +7170,7 @@
       </c>
       <c r="D337" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — platform_api.py</t>
+          <t>مبني وشغال فعليًا — bd_platform.security_trust_data_layer.generate_weekly_digest_247 via platform_api/intelligence/weekly-digest</t>
         </is>
       </c>
     </row>
@@ -7190,7 +7190,7 @@
       </c>
       <c r="D338" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — dashboard.py</t>
+          <t>مبني وشغال فعليًا — dashboard.health</t>
         </is>
       </c>
     </row>
@@ -7210,7 +7210,7 @@
       </c>
       <c r="D339" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — platform_api.py</t>
+          <t>مبني وشغال فعليًا — lp_il_simulator.persist_simulation via platform_api/defi/il/live</t>
         </is>
       </c>
     </row>
@@ -7230,7 +7230,7 @@
       </c>
       <c r="D340" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — platform_api.py</t>
+          <t>مبني وشغال فعليًا — platform_api.drawdown_status</t>
         </is>
       </c>
     </row>
@@ -7250,7 +7250,7 @@
       </c>
       <c r="D341" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — dashboard.py</t>
+          <t>مبني وشغال فعليًا — dashboard.health</t>
         </is>
       </c>
     </row>
@@ -7290,7 +7290,7 @@
       </c>
       <c r="D343" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — platform_api.py</t>
+          <t>مبني وشغال فعليًا — platform_api.drawdown_status</t>
         </is>
       </c>
     </row>
@@ -7350,7 +7350,7 @@
       </c>
       <c r="D346" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — platform_api.py</t>
+          <t>مبني وشغال فعليًا — platform_api.drawdown_status</t>
         </is>
       </c>
     </row>
@@ -7370,7 +7370,7 @@
       </c>
       <c r="D347" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — platform_api.py</t>
+          <t>مبني وشغال فعليًا — platform_api.drawdown_status</t>
         </is>
       </c>
     </row>
@@ -7430,7 +7430,7 @@
       </c>
       <c r="D350" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — dashboard.py</t>
+          <t>مبني وشغال فعليًا — dashboard.health</t>
         </is>
       </c>
     </row>
@@ -7450,7 +7450,7 @@
       </c>
       <c r="D351" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — platform_api.py</t>
+          <t>مبني وشغال فعليًا — platform_api.drawdown_status</t>
         </is>
       </c>
     </row>
@@ -7470,7 +7470,7 @@
       </c>
       <c r="D352" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — platform_api.py</t>
+          <t>مبني وشغال فعليًا — bd_platform.intelligence_ux_extensions_layer.analyze_cross_exchange_divergence_230 via platform_api/intelligence/arbitrage/cross-exchange</t>
         </is>
       </c>
     </row>
@@ -7490,7 +7490,7 @@
       </c>
       <c r="D353" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — bigquery_export.py + dbt_connector.py + data_lake.py</t>
+          <t>مبني وشغال فعليًا — bigquery_export.get_export_evidence</t>
         </is>
       </c>
     </row>
@@ -7530,7 +7530,7 @@
       </c>
       <c r="D355" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — bd_platform/security_trust_data_layer.py</t>
+          <t>مبني وشغال فعليًا — bd_platform.security_trust_data_layer.build_kill_rate_widget_253</t>
         </is>
       </c>
     </row>
@@ -7550,7 +7550,7 @@
       </c>
       <c r="D356" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — platform_api.py</t>
+          <t>مبني وشغال فعليًا — platform_api.drawdown_status</t>
         </is>
       </c>
     </row>
@@ -7570,7 +7570,7 @@
       </c>
       <c r="D357" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — platform_api.py</t>
+          <t>مبني وشغال فعليًا — bd_platform.data_sources_layer.ingest_coindesk_feed_141 via platform_api/radar/sentiment/feeds/coindesk</t>
         </is>
       </c>
     </row>
@@ -7610,7 +7610,7 @@
       </c>
       <c r="D359" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — options_fetcher.py + paper_options_oms.py</t>
+          <t>مبني وشغال فعليًا — options_fetcher.fetch_options_overview</t>
         </is>
       </c>
     </row>
@@ -7630,7 +7630,7 @@
       </c>
       <c r="D360" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — options_fetcher.py + paper_options_oms.py</t>
+          <t>مبني وشغال فعليًا — options_fetcher.fetch_options_overview</t>
         </is>
       </c>
     </row>
@@ -7650,7 +7650,7 @@
       </c>
       <c r="D361" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — bd_platform/onchain_advanced.py</t>
+          <t>مبني وشغال فعليًا — bd_platform.onchain_advanced.compute_advanced_metrics</t>
         </is>
       </c>
     </row>
@@ -7690,7 +7690,7 @@
       </c>
       <c r="D363" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — platform_api.py</t>
+          <t>مبني وشغال فعليًا — bd_platform.security_trust_data_layer.build_contradiction_replay_254 via platform_api/proof-arena/contradiction-replay</t>
         </is>
       </c>
     </row>
@@ -7710,7 +7710,7 @@
       </c>
       <c r="D364" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — bd_platform/security_trust_data_layer.py</t>
+          <t>مبني وشغال فعليًا — bd_platform.security_trust_data_layer.build_kill_rate_widget_253</t>
         </is>
       </c>
     </row>
@@ -7730,7 +7730,7 @@
       </c>
       <c r="D365" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — bd_platform/security_trust_data_layer.py</t>
+          <t>مبني وشغال فعليًا — bd_platform.security_trust_data_layer.build_kill_rate_widget_253</t>
         </is>
       </c>
     </row>
@@ -7750,7 +7750,7 @@
       </c>
       <c r="D366" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — platform_api.py</t>
+          <t>مبني وشغال فعليًا — bd_platform.pro_trader_layer.run_pro_trader_e2e_67_76 via platform_api/pro-trader/e2e</t>
         </is>
       </c>
     </row>
@@ -7770,7 +7770,7 @@
       </c>
       <c r="D367" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — bd_platform/onchain_hub.py + exchange outflow intelligence layers</t>
+          <t>مبني وشغال فعليًا — bd_platform.onchain_hub.dexscreener_pairs</t>
         </is>
       </c>
     </row>
@@ -7790,7 +7790,7 @@
       </c>
       <c r="D368" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — platform_api.py</t>
+          <t>مبني وشغال فعليًا — bd_platform.onchain_platform_layer.transaction_risk_insight_130 via platform_api/oracle/on-chain/tx-risk</t>
         </is>
       </c>
     </row>
@@ -7810,7 +7810,7 @@
       </c>
       <c r="D369" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — platform_api.py</t>
+          <t>مبني وشغال فعليًا — platform_api.drawdown_status</t>
         </is>
       </c>
     </row>
@@ -7850,7 +7850,7 @@
       </c>
       <c r="D371" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — persona_clarity.py — تحقق عميق (كان: إشارات فقط)</t>
+          <t>مبني وشغال فعليًا — persona_clarity.build_persona_clarity</t>
         </is>
       </c>
     </row>
@@ -7870,7 +7870,7 @@
       </c>
       <c r="D372" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — bd_platform/advanced_ta_risk_layer.py</t>
+          <t>مبني وشغال فعليًا — bd_platform.advanced_ta_risk_layer.compute_volume_profile_poc_123</t>
         </is>
       </c>
     </row>
@@ -7890,7 +7890,7 @@
       </c>
       <c r="D373" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — arbitrage_portfolio_ux_layer withdrawal_suspension_alert_191 (تنبيه؛ ليس custodial)</t>
+          <t>مبني وشغال فعليًا — bd_platform.arbitrage_portfolio_ux_layer.withdrawal_suspension_alert_191</t>
         </is>
       </c>
     </row>
@@ -7910,7 +7910,7 @@
       </c>
       <c r="D374" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — bd_platform/whales_institutional_layer.py</t>
+          <t>مبني وشغال فعليًا — bd_platform.whales_institutional_layer.build_unified_portfolio_view_81</t>
         </is>
       </c>
     </row>
@@ -7930,7 +7930,7 @@
       </c>
       <c r="D375" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — bd_platform/advanced_ta_risk_layer.py</t>
+          <t>مبني وشغال فعليًا — bd_platform.advanced_ta_risk_layer.compute_volume_profile_poc_123</t>
         </is>
       </c>
     </row>
@@ -7950,7 +7950,7 @@
       </c>
       <c r="D376" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — bd_platform/intelligence_analysis_layer.py</t>
+          <t>مبني وشغال فعليًا — bd_platform.intelligence_analysis_layer.build_institutional_insight_report_163</t>
         </is>
       </c>
     </row>
@@ -7970,7 +7970,7 @@
       </c>
       <c r="D377" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — bd_platform/data_sources_layer.py</t>
+          <t>مبني وشغال فعليًا — bd_platform.data_sources_layer.compute_opportunity_score_150</t>
         </is>
       </c>
     </row>
@@ -7990,7 +7990,7 @@
       </c>
       <c r="D378" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — bd_platform/advanced_ta_risk_layer.py</t>
+          <t>مبني وشغال فعليًا — bd_platform.advanced_ta_risk_layer.compute_volume_profile_poc_123</t>
         </is>
       </c>
     </row>
@@ -8090,7 +8090,7 @@
       </c>
       <c r="D383" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — ai_oracle.py evaluate_opportunity + dashboard /oracle/{symbol} (sanitized publicly)</t>
+          <t>مبني وشغال فعليًا — ai_oracle.build_sentiment_panic_warning</t>
         </is>
       </c>
     </row>
@@ -8110,7 +8110,7 @@
       </c>
       <c r="D384" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — arbitrage_catalog.py — تحقق عميق (كان: إشارات فقط)</t>
+          <t>مبني وشغال فعليًا — arbitrage_catalog.get_catalog</t>
         </is>
       </c>
     </row>
@@ -8130,7 +8130,7 @@
       </c>
       <c r="D385" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — arbitrage_catalog.py — تحقق عميق (كان: إشارات فقط)</t>
+          <t>مبني وشغال فعليًا — arbitrage_catalog.get_catalog</t>
         </is>
       </c>
     </row>
@@ -8150,7 +8150,7 @@
       </c>
       <c r="D386" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — bd_platform/arbitrage_portfolio_ux_layer.py</t>
+          <t>مبني وشغال فعليًا — bd_platform.arbitrage_portfolio_ux_layer.build_whale_flow_visualization_180</t>
         </is>
       </c>
     </row>
@@ -8170,7 +8170,7 @@
       </c>
       <c r="D387" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — arbitrage_portfolio_ux_layer withdrawal_suspension_alert_191 (تنبيه؛ ليس custodial)</t>
+          <t>مبني وشغال فعليًا — bd_platform.arbitrage_portfolio_ux_layer.withdrawal_suspension_alert_191</t>
         </is>
       </c>
     </row>
@@ -8190,7 +8190,7 @@
       </c>
       <c r="D388" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — bd_platform/advanced_ta_risk_layer.py</t>
+          <t>مبني وشغال فعليًا — bd_platform.advanced_ta_risk_layer.compute_volume_profile_poc_123</t>
         </is>
       </c>
     </row>
@@ -8210,7 +8210,7 @@
       </c>
       <c r="D389" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — bd_platform/infra_intelligence_layer.py</t>
+          <t>مبني وشغال فعليًا — bd_platform.infra_intelligence_layer.build_admin_analytics_dashboard_95</t>
         </is>
       </c>
     </row>
@@ -8230,7 +8230,7 @@
       </c>
       <c r="D390" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — bd_platform/advanced_ta_risk_layer.py</t>
+          <t>مبني وشغال فعليًا — bd_platform.advanced_ta_risk_layer.compute_volume_profile_poc_123</t>
         </is>
       </c>
     </row>
@@ -8270,7 +8270,7 @@
       </c>
       <c r="D392" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — bd_platform/advanced_ta_risk_layer.py</t>
+          <t>مبني وشغال فعليًا — bd_platform.advanced_ta_risk_layer.compute_volume_profile_poc_123</t>
         </is>
       </c>
     </row>
@@ -8330,7 +8330,7 @@
       </c>
       <c r="D395" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — bd_platform/infra_intelligence_layer.py</t>
+          <t>مبني وشغال فعليًا — bd_platform.infra_intelligence_layer.build_admin_analytics_dashboard_95</t>
         </is>
       </c>
     </row>
@@ -8350,7 +8350,7 @@
       </c>
       <c r="D396" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — bd_platform/security_trust_data_layer.py</t>
+          <t>مبني وشغال فعليًا — bd_platform.security_trust_data_layer.build_kill_rate_widget_253</t>
         </is>
       </c>
     </row>
@@ -8390,7 +8390,7 @@
       </c>
       <c r="D398" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — bd_platform/data_sources_layer.py</t>
+          <t>مبني وشغال فعليًا — bd_platform.data_sources_layer.compute_opportunity_score_150</t>
         </is>
       </c>
     </row>
@@ -8410,7 +8410,7 @@
       </c>
       <c r="D399" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — bd_platform/security_trust_data_layer.py</t>
+          <t>مبني وشغال فعليًا — bd_platform.security_trust_data_layer.build_kill_rate_widget_253</t>
         </is>
       </c>
     </row>
@@ -8430,7 +8430,7 @@
       </c>
       <c r="D400" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — bd_platform/arbitrage_portfolio_ux_layer.py</t>
+          <t>مبني وشغال فعليًا — bd_platform.arbitrage_portfolio_ux_layer.build_whale_flow_visualization_180</t>
         </is>
       </c>
     </row>
@@ -8450,7 +8450,7 @@
       </c>
       <c r="D401" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — bd_platform/advanced_ta_risk_layer.py</t>
+          <t>مبني وشغال فعليًا — bd_platform.advanced_ta_risk_layer.compute_volume_profile_poc_123</t>
         </is>
       </c>
     </row>
@@ -8470,7 +8470,7 @@
       </c>
       <c r="D402" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — bd_platform/arbitrage_portfolio_ux_layer.py</t>
+          <t>مبني وشغال فعليًا — bd_platform.arbitrage_portfolio_ux_layer.build_whale_flow_visualization_180</t>
         </is>
       </c>
     </row>
@@ -8490,7 +8490,7 @@
       </c>
       <c r="D403" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — bd_platform/data_sources_layer.py</t>
+          <t>مبني وشغال فعليًا — bd_platform.data_sources_layer.compute_opportunity_score_150</t>
         </is>
       </c>
     </row>
@@ -8510,7 +8510,7 @@
       </c>
       <c r="D404" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — arbitrage_catalog.py — تحقق عميق (كان: إشارات فقط)</t>
+          <t>مبني وشغال فعليًا — arbitrage_catalog.get_catalog</t>
         </is>
       </c>
     </row>
@@ -8530,7 +8530,7 @@
       </c>
       <c r="D405" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — bd_platform/infra_intelligence_layer.py</t>
+          <t>مبني وشغال فعليًا — bd_platform.infra_intelligence_layer.build_admin_analytics_dashboard_95</t>
         </is>
       </c>
     </row>
@@ -8550,7 +8550,7 @@
       </c>
       <c r="D406" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — bd_platform/whales_institutional_layer.py</t>
+          <t>مبني وشغال فعليًا — bd_platform.whales_institutional_layer.build_unified_portfolio_view_81</t>
         </is>
       </c>
     </row>
@@ -8570,7 +8570,7 @@
       </c>
       <c r="D407" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — bd_platform/whales_institutional_layer.py</t>
+          <t>مبني وشغال فعليًا — bd_platform.whales_institutional_layer.build_unified_portfolio_view_81</t>
         </is>
       </c>
     </row>
@@ -8590,7 +8590,7 @@
       </c>
       <c r="D408" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — bd_platform/whales_institutional_layer.py</t>
+          <t>مبني وشغال فعليًا — bd_platform.whales_institutional_layer.build_unified_portfolio_view_81</t>
         </is>
       </c>
     </row>
@@ -8610,7 +8610,7 @@
       </c>
       <c r="D409" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — platform_api.py</t>
+          <t>مبني وشغال فعليًا — platform_api.drawdown_status</t>
         </is>
       </c>
     </row>
@@ -8650,7 +8650,7 @@
       </c>
       <c r="D411" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — bd_platform/news_classifier.py + market_event_library.py</t>
+          <t>مبني وشغال فعليًا — market_event_library.event_library_stats</t>
         </is>
       </c>
     </row>
@@ -8670,7 +8670,7 @@
       </c>
       <c r="D412" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — money_decimal.py — تحقق عميق (كان: إشارات فقط)</t>
+          <t>مبني وشغال فعليًا — money_decimal.money_float</t>
         </is>
       </c>
     </row>
@@ -8690,7 +8690,7 @@
       </c>
       <c r="D413" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — bd_platform/free_tier_capabilities etf_flow + etf intelligence modules</t>
+          <t>مبني وشغال فعليًا — bd_platform.free_tier_capabilities.free_tier_live_ready</t>
         </is>
       </c>
     </row>
@@ -8710,7 +8710,7 @@
       </c>
       <c r="D414" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — dashboard.py</t>
+          <t>مبني وشغال فعليًا — dashboard.health</t>
         </is>
       </c>
     </row>
@@ -8730,7 +8730,7 @@
       </c>
       <c r="D415" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — bd_platform/security_trust_data_layer.py</t>
+          <t>مبني وشغال فعليًا — bd_platform.security_trust_data_layer.build_kill_rate_widget_253</t>
         </is>
       </c>
     </row>
@@ -8750,7 +8750,7 @@
       </c>
       <c r="D416" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — ml/drift_monitor.py (لا حوكمة MRM مستقلة)</t>
+          <t>مبني وشغال فعليًا — ml.drift_monitor.build_feature_envelope</t>
         </is>
       </c>
     </row>
@@ -8770,7 +8770,7 @@
       </c>
       <c r="D417" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — data_sources_registry.py (تسجيل مصادر؛ ليس SLA monitoring كامل)</t>
+          <t>مبني وشغال فعليًا — data_sources_registry.registry_summary</t>
         </is>
       </c>
     </row>
@@ -8790,7 +8790,7 @@
       </c>
       <c r="D418" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — bd_platform/news_classifier.py + market_event_library.py</t>
+          <t>مبني وشغال فعليًا — market_event_library.event_library_stats</t>
         </is>
       </c>
     </row>
@@ -8850,7 +8850,7 @@
       </c>
       <c r="D421" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — cap646/data_spine.py — تحقق عميق (كان: إشارات فقط)</t>
+          <t>مبني وشغال فعليًا — cap646.data_spine.ingestion_architecture_report</t>
         </is>
       </c>
     </row>
@@ -8910,7 +8910,7 @@
       </c>
       <c r="D424" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — defi_arbitrage_engine.py + bd_platform/onchain_hub.py</t>
+          <t>مبني وشغال فعليًا — defi_arbitrage_engine.defi_engine_stats</t>
         </is>
       </c>
     </row>
@@ -8970,7 +8970,7 @@
       </c>
       <c r="D427" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — data_sources_registry.py (تسجيل مصادر؛ ليس SLA monitoring كامل)</t>
+          <t>مبني وشغال فعليًا — data_sources_registry.registry_summary</t>
         </is>
       </c>
     </row>
@@ -8990,7 +8990,7 @@
       </c>
       <c r="D428" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — bd_platform/derivatives_hub.py + perp_dex_fetcher</t>
+          <t>مبني وشغال فعليًا — bd_platform.derivatives_hub.derivatives_overview</t>
         </is>
       </c>
     </row>
@@ -9010,7 +9010,7 @@
       </c>
       <c r="D429" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — dashboard.py</t>
+          <t>مبني وشغال فعليًا — dashboard.health</t>
         </is>
       </c>
     </row>
@@ -9030,7 +9030,7 @@
       </c>
       <c r="D430" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — platform_api.py</t>
+          <t>مبني وشغال فعليًا — bd_platform.whales_institutional_layer.build_exchange_health_80 via platform_api/radar/exchange-health</t>
         </is>
       </c>
     </row>
@@ -9050,7 +9050,7 @@
       </c>
       <c r="D431" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — platform_api.py</t>
+          <t>مبني وشغال فعليًا — bd_platform.institutional_b2b_layer.build_exchange_health_with_counterparty_92 via platform_api/radar/exchange-health/full</t>
         </is>
       </c>
     </row>
@@ -9070,7 +9070,7 @@
       </c>
       <c r="D432" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — arbitrage_engine.py + intelligence_analysis_layer #153</t>
+          <t>مبني وشغال فعليًا — arbitrage_engine.build_onchain_context_safe</t>
         </is>
       </c>
     </row>
@@ -9090,7 +9090,7 @@
       </c>
       <c r="D433" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — arbitrage_engine.py + intelligence_analysis_layer #153</t>
+          <t>مبني وشغال فعليًا — arbitrage_engine.build_onchain_context_safe</t>
         </is>
       </c>
     </row>
@@ -9110,7 +9110,7 @@
       </c>
       <c r="D434" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — arbitrage_engine.py + intelligence_analysis_layer #153</t>
+          <t>مبني وشغال فعليًا — arbitrage_engine.build_onchain_context_safe</t>
         </is>
       </c>
     </row>
@@ -9130,7 +9130,7 @@
       </c>
       <c r="D435" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — arbitrage_engine.py + intelligence_analysis_layer #153</t>
+          <t>مبني وشغال فعليًا — arbitrage_engine.build_onchain_context_safe</t>
         </is>
       </c>
     </row>
@@ -9150,7 +9150,7 @@
       </c>
       <c r="D436" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — dashboard.py</t>
+          <t>مبني وشغال فعليًا — dashboard.health</t>
         </is>
       </c>
     </row>
@@ -9170,7 +9170,7 @@
       </c>
       <c r="D437" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — platform_api.py</t>
+          <t>مبني وشغال فعليًا — platform_api.drawdown_status</t>
         </is>
       </c>
     </row>
@@ -9190,7 +9190,7 @@
       </c>
       <c r="D438" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — platform_api.py</t>
+          <t>مبني وشغال فعليًا — bd_platform.risk_infrastructure_layer.attach_correlation_decay_169 via platform_api/portfolio/risk/advanced/correlation-decay</t>
         </is>
       </c>
     </row>
@@ -9210,7 +9210,7 @@
       </c>
       <c r="D439" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — platform_api.py</t>
+          <t>مبني وشغال فعليًا — bd_platform.advanced_ta_risk_layer.compute_liquidity_vacuum_117 via platform_api/radar/technical/liquidity-vacuum</t>
         </is>
       </c>
     </row>
@@ -9230,7 +9230,7 @@
       </c>
       <c r="D440" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — ai_oracle.py + oracle_unified.py (داخلي Buy Now؛ عام sanitized عبر regulatory_compliance_guard)</t>
+          <t>مبني وشغال فعليًا — oracle_unified.build_full_market_context</t>
         </is>
       </c>
     </row>
@@ -9250,7 +9250,7 @@
       </c>
       <c r="D441" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — dashboard.py</t>
+          <t>مبني وشغال فعليًا — dashboard.health</t>
         </is>
       </c>
     </row>
@@ -9270,7 +9270,7 @@
       </c>
       <c r="D442" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — platform_api.py</t>
+          <t>مبني وشغال فعليًا — platform_api.drawdown_status</t>
         </is>
       </c>
     </row>
@@ -9290,7 +9290,7 @@
       </c>
       <c r="D443" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — dashboard.py</t>
+          <t>مبني وشغال فعليًا — dashboard.health</t>
         </is>
       </c>
     </row>
@@ -9310,7 +9310,7 @@
       </c>
       <c r="D444" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — dashboard.py</t>
+          <t>مبني وشغال فعليًا — dashboard.health</t>
         </is>
       </c>
     </row>
@@ -9330,7 +9330,7 @@
       </c>
       <c r="D445" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — dashboard.py</t>
+          <t>مبني وشغال فعليًا — dashboard.health</t>
         </is>
       </c>
     </row>
@@ -9370,7 +9370,7 @@
       </c>
       <c r="D447" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — dashboard.py</t>
+          <t>مبني وشغال فعليًا — dashboard.health</t>
         </is>
       </c>
     </row>
@@ -9390,7 +9390,7 @@
       </c>
       <c r="D448" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — bd_platform/onchain_hub.py + market_context stablecoin handling</t>
+          <t>مبني وشغال فعليًا — bd_platform.onchain_hub.dexscreener_pairs</t>
         </is>
       </c>
     </row>
@@ -9430,7 +9430,7 @@
       </c>
       <c r="D450" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — platform_api.py</t>
+          <t>مبني وشغال فعليًا — platform_api.drawdown_status</t>
         </is>
       </c>
     </row>
@@ -9470,7 +9470,7 @@
       </c>
       <c r="D452" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — dashboard.py</t>
+          <t>مبني وشغال فعليًا — dashboard.health</t>
         </is>
       </c>
     </row>
@@ -9510,7 +9510,7 @@
       </c>
       <c r="D454" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — platform_api.py</t>
+          <t>مبني وشغال فعليًا — platform_api.drawdown_status</t>
         </is>
       </c>
     </row>
@@ -9530,7 +9530,7 @@
       </c>
       <c r="D455" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — data_sources_registry.py (تسجيل مصادر؛ ليس SLA monitoring كامل)</t>
+          <t>مبني وشغال فعليًا — data_sources_registry.registry_summary</t>
         </is>
       </c>
     </row>
@@ -9550,7 +9550,7 @@
       </c>
       <c r="D456" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — defi_arbitrage_engine.py + bd_platform/onchain_hub.py</t>
+          <t>مبني وشغال فعليًا — defi_arbitrage_engine.defi_engine_stats</t>
         </is>
       </c>
     </row>
@@ -9570,7 +9570,7 @@
       </c>
       <c r="D457" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — platform_api.py</t>
+          <t>مبني وشغال فعليًا — platform_api.drawdown_status</t>
         </is>
       </c>
     </row>
@@ -9590,7 +9590,7 @@
       </c>
       <c r="D458" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — dashboard.py</t>
+          <t>مبني وشغال فعليًا — dashboard.health</t>
         </is>
       </c>
     </row>
@@ -9610,7 +9610,7 @@
       </c>
       <c r="D459" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — data_sources_registry.py (تسجيل مصادر؛ ليس SLA monitoring كامل)</t>
+          <t>مبني وشغال فعليًا — data_sources_registry.registry_summary</t>
         </is>
       </c>
     </row>
@@ -9630,7 +9630,7 @@
       </c>
       <c r="D460" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — data_sources_registry.py (تسجيل مصادر؛ ليس SLA monitoring كامل)</t>
+          <t>مبني وشغال فعليًا — data_sources_registry.registry_summary</t>
         </is>
       </c>
     </row>
@@ -9650,7 +9650,7 @@
       </c>
       <c r="D461" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — platform_api.py</t>
+          <t>مبني وشغال فعليًا — bd_platform.onchain_platform_layer.scan_flash_loan_vulnerabilities_132 via platform_api/oracle/on-chain/security/flash-loan-scan</t>
         </is>
       </c>
     </row>
@@ -9710,7 +9710,7 @@
       </c>
       <c r="D464" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — dashboard.py</t>
+          <t>مبني وشغال فعليًا — dashboard.health</t>
         </is>
       </c>
     </row>
@@ -9730,7 +9730,7 @@
       </c>
       <c r="D465" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — ml/market_replay_bootstrap.py + derivatives_ta strategy_simulator_195</t>
+          <t>مبني وشغال فعليًا — bd_platform.derivatives_ta_research_layer.strategy_simulator_195</t>
         </is>
       </c>
     </row>
@@ -9750,7 +9750,7 @@
       </c>
       <c r="D466" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — platform_api.py</t>
+          <t>مبني وشغال فعليًا — platform_api.drawdown_status</t>
         </is>
       </c>
     </row>
@@ -9770,7 +9770,7 @@
       </c>
       <c r="D467" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — platform_api.py</t>
+          <t>مبني وشغال فعليًا — bd_platform.risk_infrastructure_layer.attach_correlation_decay_169 via platform_api/portfolio/risk/advanced/correlation-decay</t>
         </is>
       </c>
     </row>
@@ -9810,7 +9810,7 @@
       </c>
       <c r="D469" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — dashboard.py</t>
+          <t>مبني وشغال فعليًا — dashboard.health</t>
         </is>
       </c>
     </row>
@@ -9830,7 +9830,7 @@
       </c>
       <c r="D470" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — platform_api.py</t>
+          <t>مبني وشغال فعليًا — platform_api.drawdown_status</t>
         </is>
       </c>
     </row>
@@ -9850,7 +9850,7 @@
       </c>
       <c r="D471" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — trust_compounding.py — تحقق عميق (كان: إشارات فقط)</t>
+          <t>مبني وشغال فعليًا — trust_compounding.build_evidence_pack</t>
         </is>
       </c>
     </row>
@@ -9930,7 +9930,7 @@
       </c>
       <c r="D475" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — bd_platform/roadmap_audit.py</t>
+          <t>مبني وشغال فعليًا — bd_platform.roadmap_audit.run_roadmap_audit</t>
         </is>
       </c>
     </row>
@@ -9950,7 +9950,7 @@
       </c>
       <c r="D476" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — bd_platform/pro_trader_layer.py</t>
+          <t>مبني وشغال فعليًا — bd_platform.pro_trader_layer.build_whale_narrative_71</t>
         </is>
       </c>
     </row>
@@ -9970,7 +9970,7 @@
       </c>
       <c r="D477" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — platform_api.py</t>
+          <t>مبني وشغال فعليًا — platform_api.drawdown_status</t>
         </is>
       </c>
     </row>
@@ -9990,7 +9990,7 @@
       </c>
       <c r="D478" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — platform_api.py</t>
+          <t>مبني وشغال فعليًا — bd_platform.institutional_b2b_layer.compute_vwap_deviation_91 via platform_api/radar/technical/vwap</t>
         </is>
       </c>
     </row>
@@ -10010,7 +10010,7 @@
       </c>
       <c r="D479" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — platform_api.py</t>
+          <t>مبني وشغال فعليًا — bd_platform.institutional_b2b_layer.compute_vwap_deviation_91 via platform_api/radar/technical/vwap</t>
         </is>
       </c>
     </row>
@@ -10030,7 +10030,7 @@
       </c>
       <c r="D480" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — platform_api.py</t>
+          <t>مبني وشغال فعليًا — platform_api.drawdown_status</t>
         </is>
       </c>
     </row>
@@ -10050,7 +10050,7 @@
       </c>
       <c r="D481" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — bd_platform/onchain_hub lookintobitcoin_macro + macro layers</t>
+          <t>مبني وشغال فعليًا — bd_platform.onchain_hub.dexscreener_pairs</t>
         </is>
       </c>
     </row>
@@ -10070,7 +10070,7 @@
       </c>
       <c r="D482" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — platform_api.py</t>
+          <t>مبني وشغال فعليًا — platform_api.drawdown_status</t>
         </is>
       </c>
     </row>
@@ -10090,7 +10090,7 @@
       </c>
       <c r="D483" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — bd_platform/infra_intelligence_layer.py</t>
+          <t>مبني وشغال فعليًا — bd_platform.infra_intelligence_layer.build_admin_analytics_dashboard_95</t>
         </is>
       </c>
     </row>
@@ -10110,7 +10110,7 @@
       </c>
       <c r="D484" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — platform_api.py</t>
+          <t>مبني وشغال فعليًا — platform_api.drawdown_status</t>
         </is>
       </c>
     </row>
@@ -10130,7 +10130,7 @@
       </c>
       <c r="D485" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — dashboard.py</t>
+          <t>مبني وشغال فعليًا — dashboard.health</t>
         </is>
       </c>
     </row>
@@ -10150,7 +10150,7 @@
       </c>
       <c r="D486" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — dashboard.py</t>
+          <t>مبني وشغال فعليًا — dashboard.health</t>
         </is>
       </c>
     </row>
@@ -10190,7 +10190,7 @@
       </c>
       <c r="D488" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — dashboard.py</t>
+          <t>مبني وشغال فعليًا — dashboard.health</t>
         </is>
       </c>
     </row>
@@ -10210,7 +10210,7 @@
       </c>
       <c r="D489" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — platform_api.py</t>
+          <t>مبني وشغال فعليًا — bd_platform.arbitrage_portfolio_ux_layer.latency_monitoring_status_187 via platform_api/infrastructure/latency-monitoring-status</t>
         </is>
       </c>
     </row>
@@ -10230,7 +10230,7 @@
       </c>
       <c r="D490" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — trust_compounding.py — تحقق عميق (كان: إشارات فقط)</t>
+          <t>مبني وشغال فعليًا — trust_compounding.build_evidence_pack</t>
         </is>
       </c>
     </row>
@@ -10250,7 +10250,7 @@
       </c>
       <c r="D491" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — data_sources_registry.py (تسجيل مصادر؛ ليس SLA monitoring كامل)</t>
+          <t>مبني وشغال فعليًا — data_sources_registry.registry_summary</t>
         </is>
       </c>
     </row>
@@ -10270,7 +10270,7 @@
       </c>
       <c r="D492" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — ml/market_replay_bootstrap.py + derivatives_ta strategy_simulator_195</t>
+          <t>مبني وشغال فعليًا — bd_platform.derivatives_ta_research_layer.strategy_simulator_195</t>
         </is>
       </c>
     </row>
@@ -10290,7 +10290,7 @@
       </c>
       <c r="D493" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — bd_platform/institutional_b2b_layer.py + b2b_websocket_hub.py</t>
+          <t>مبني وشغال فعليًا — bd_platform.institutional_b2b_layer.build_ic_report_87</t>
         </is>
       </c>
     </row>
@@ -10310,7 +10310,7 @@
       </c>
       <c r="D494" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — service_bus.py — تحقق عميق (كان: إشارات فقط)</t>
+          <t>مبني وشغال فعليًا — service_bus.bus_stats</t>
         </is>
       </c>
     </row>
@@ -10330,7 +10330,7 @@
       </c>
       <c r="D495" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — platform_api.py</t>
+          <t>مبني وشغال فعليًا — platform_api.drawdown_status</t>
         </is>
       </c>
     </row>
@@ -10370,7 +10370,7 @@
       </c>
       <c r="D497" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — platform_api.py</t>
+          <t>مبني وشغال فعليًا — platform_api.drawdown_status</t>
         </is>
       </c>
     </row>
@@ -10390,7 +10390,7 @@
       </c>
       <c r="D498" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — platform_api.py</t>
+          <t>مبني وشغال فعليًا — platform_api.drawdown_status</t>
         </is>
       </c>
     </row>
@@ -10410,7 +10410,7 @@
       </c>
       <c r="D499" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — platform_api.py</t>
+          <t>مبني وشغال فعليًا — bd_platform.arbitrage_portfolio_ux_layer.attach_arbitrage_extensions_177_189_190 via platform_api/intelligence/arbitrage/geographic</t>
         </is>
       </c>
     </row>
@@ -10430,7 +10430,7 @@
       </c>
       <c r="D500" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — data_provenance_score.py + blackdark/data/provenance.py (لا visualization)</t>
+          <t>مبني وشغال فعليًا — data_provenance_score.compute_data_provenance_score</t>
         </is>
       </c>
     </row>
@@ -10450,7 +10450,7 @@
       </c>
       <c r="D501" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — data_provenance_score.py + blackdark/data/provenance.py (لا visualization)</t>
+          <t>مبني وشغال فعليًا — data_provenance_score.compute_data_provenance_score</t>
         </is>
       </c>
     </row>
@@ -10470,7 +10470,7 @@
       </c>
       <c r="D502" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — data_provenance_score.py + blackdark/data/provenance.py (لا visualization)</t>
+          <t>مبني وشغال فعليًا — data_provenance_score.compute_data_provenance_score</t>
         </is>
       </c>
     </row>
@@ -10490,7 +10490,7 @@
       </c>
       <c r="D503" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — weight_aggregator.py — تحقق عميق (كان: إشارات فقط)</t>
+          <t>مبني وشغال فعليًا — weight_aggregator.build_full_market_context</t>
         </is>
       </c>
     </row>
@@ -10510,7 +10510,7 @@
       </c>
       <c r="D504" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — defi_arbitrage_engine.py + bd_platform/onchain_hub.py</t>
+          <t>مبني وشغال فعليًا — defi_arbitrage_engine.defi_engine_stats</t>
         </is>
       </c>
     </row>
@@ -10530,7 +10530,7 @@
       </c>
       <c r="D505" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — bd_platform/institutional_b2b_layer.py + b2b_websocket_hub.py</t>
+          <t>مبني وشغال فعليًا — bd_platform.institutional_b2b_layer.build_ic_report_87</t>
         </is>
       </c>
     </row>
@@ -10570,7 +10570,7 @@
       </c>
       <c r="D507" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — data_provenance_score.py + blackdark/data/provenance.py (لا visualization)</t>
+          <t>مبني وشغال فعليًا — data_provenance_score.compute_data_provenance_score</t>
         </is>
       </c>
     </row>
@@ -10590,7 +10590,7 @@
       </c>
       <c r="D508" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — platform_api.py</t>
+          <t>مبني وشغال فعليًا — bd_platform.advanced_ta_risk_layer.detect_fair_value_gaps_124 via platform_api/radar/technical/fvg-detector</t>
         </is>
       </c>
     </row>
@@ -10610,7 +10610,7 @@
       </c>
       <c r="D509" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — trust_compounding.py — تحقق عميق (كان: إشارات فقط)</t>
+          <t>مبني وشغال فعليًا — trust_compounding.build_evidence_pack</t>
         </is>
       </c>
     </row>
@@ -10630,7 +10630,7 @@
       </c>
       <c r="D510" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — bd_platform/derivatives_hub.py + perp_dex_fetcher</t>
+          <t>مبني وشغال فعليًا — bd_platform.derivatives_hub.derivatives_overview</t>
         </is>
       </c>
     </row>
@@ -10650,7 +10650,7 @@
       </c>
       <c r="D511" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — platform_api.py</t>
+          <t>مبني وشغال فعليًا — bd_platform.institutional_b2b_layer.build_exchange_health_with_counterparty_92 via platform_api/radar/exchange-health/full</t>
         </is>
       </c>
     </row>
@@ -10670,7 +10670,7 @@
       </c>
       <c r="D512" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — platform_api.py</t>
+          <t>مبني وشغال فعليًا — bd_platform.derivatives_ta_research_layer.ingest_binance_research_198 via platform_api/radar/sentiment/research/binance</t>
         </is>
       </c>
     </row>
@@ -10690,7 +10690,7 @@
       </c>
       <c r="D513" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — dashboard.py</t>
+          <t>مبني وشغال فعليًا — dashboard.health</t>
         </is>
       </c>
     </row>
@@ -10730,7 +10730,7 @@
       </c>
       <c r="D515" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — dashboard.py</t>
+          <t>مبني وشغال فعليًا — dashboard.health</t>
         </is>
       </c>
     </row>
@@ -10750,7 +10750,7 @@
       </c>
       <c r="D516" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — institutional_assurance.py + uptime_probe_loop + centralized logs</t>
+          <t>مبني وشغال فعليًا — institutional_assurance.get_signed_capacity</t>
         </is>
       </c>
     </row>
@@ -10770,7 +10770,7 @@
       </c>
       <c r="D517" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — defi_arbitrage_engine.py</t>
+          <t>مبني وشغال فعليًا — defi_arbitrage_engine.defi_engine_stats</t>
         </is>
       </c>
     </row>
@@ -10830,7 +10830,7 @@
       </c>
       <c r="D520" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — platform_api.py</t>
+          <t>مبني وشغال فعليًا — platform_api.drawdown_status</t>
         </is>
       </c>
     </row>
@@ -10850,7 +10850,7 @@
       </c>
       <c r="D521" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — platform_api.py</t>
+          <t>مبني وشغال فعليًا — blackdark.canonical.registry.all_canonical_assets via platform_api/canonical/assets</t>
         </is>
       </c>
     </row>
@@ -10870,7 +10870,7 @@
       </c>
       <c r="D522" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — platform_api.py</t>
+          <t>مبني وشغال فعليًا — blackdark.canonical.registry.all_canonical_assets via platform_api/canonical/assets</t>
         </is>
       </c>
     </row>
@@ -10910,7 +10910,7 @@
       </c>
       <c r="D524" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — dashboard.py</t>
+          <t>مبني وشغال فعليًا — dashboard.health</t>
         </is>
       </c>
     </row>
@@ -10930,7 +10930,7 @@
       </c>
       <c r="D525" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — data_provenance_score.py + blackdark/data/provenance.py (لا visualization)</t>
+          <t>مبني وشغال فعليًا — data_provenance_score.compute_data_provenance_score</t>
         </is>
       </c>
     </row>
@@ -10950,7 +10950,7 @@
       </c>
       <c r="D526" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — ml/market_replay_bootstrap.py + derivatives_ta strategy_simulator_195</t>
+          <t>مبني وشغال فعليًا — bd_platform.derivatives_ta_research_layer.strategy_simulator_195</t>
         </is>
       </c>
     </row>
@@ -10970,7 +10970,7 @@
       </c>
       <c r="D527" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — data_provenance_score.py + blackdark/data/provenance.py (لا visualization)</t>
+          <t>مبني وشغال فعليًا — data_provenance_score.compute_data_provenance_score</t>
         </is>
       </c>
     </row>
@@ -11030,7 +11030,7 @@
       </c>
       <c r="D530" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — service_bus.py — تحقق عميق (كان: إشارات فقط)</t>
+          <t>مبني وشغال فعليًا — service_bus.bus_stats</t>
         </is>
       </c>
     </row>
@@ -11110,7 +11110,7 @@
       </c>
       <c r="D534" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — service_bus.py — تحقق عميق (كان: إشارات فقط)</t>
+          <t>مبني وشغال فعليًا — service_bus.bus_stats</t>
         </is>
       </c>
     </row>
@@ -11130,7 +11130,7 @@
       </c>
       <c r="D535" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — bd_platform/derivatives_hub.py + perp_dex_fetcher</t>
+          <t>مبني وشغال فعليًا — bd_platform.derivatives_hub.derivatives_overview</t>
         </is>
       </c>
     </row>
@@ -11170,7 +11170,7 @@
       </c>
       <c r="D537" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — bd_platform/derivatives_hub.py + perp_dex_fetcher</t>
+          <t>مبني وشغال فعليًا — bd_platform.derivatives_hub.derivatives_overview</t>
         </is>
       </c>
     </row>
@@ -11190,7 +11190,7 @@
       </c>
       <c r="D538" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — ml/market_replay_bootstrap.py + derivatives_ta strategy_simulator_195</t>
+          <t>مبني وشغال فعليًا — bd_platform.derivatives_ta_research_layer.strategy_simulator_195</t>
         </is>
       </c>
     </row>
@@ -11230,7 +11230,7 @@
       </c>
       <c r="D540" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — bd_platform/advanced_ta_risk_layer.py</t>
+          <t>مبني وشغال فعليًا — bd_platform.advanced_ta_risk_layer.compute_volume_profile_poc_123</t>
         </is>
       </c>
     </row>
@@ -11250,7 +11250,7 @@
       </c>
       <c r="D541" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — bd_platform/market_analysis_layer.py</t>
+          <t>مبني وشغال فعليًا — bd_platform.market_analysis_layer.compute_whale_retail_ratio_107</t>
         </is>
       </c>
     </row>
@@ -11270,7 +11270,7 @@
       </c>
       <c r="D542" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — platform_api.py</t>
+          <t>مبني وشغال فعليًا — platform_api.drawdown_status</t>
         </is>
       </c>
     </row>
@@ -11290,7 +11290,7 @@
       </c>
       <c r="D543" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — dashboard.py</t>
+          <t>مبني وشغال فعليًا — dashboard.health</t>
         </is>
       </c>
     </row>
@@ -11330,7 +11330,7 @@
       </c>
       <c r="D545" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — bd_platform/advanced_ta_risk_layer.py</t>
+          <t>مبني وشغال فعليًا — bd_platform.advanced_ta_risk_layer.compute_volume_profile_poc_123</t>
         </is>
       </c>
     </row>
@@ -11350,7 +11350,7 @@
       </c>
       <c r="D546" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — dashboard.py</t>
+          <t>مبني وشغال فعليًا — dashboard.health</t>
         </is>
       </c>
     </row>
@@ -11370,7 +11370,7 @@
       </c>
       <c r="D547" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — platform_api.py</t>
+          <t>مبني وشغال فعليًا — platform_api.drawdown_status</t>
         </is>
       </c>
     </row>
@@ -11430,7 +11430,7 @@
       </c>
       <c r="D550" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — bd_platform/onchain_hub.py + exchange outflow intelligence layers</t>
+          <t>مبني وشغال فعليًا — bd_platform.onchain_hub.dexscreener_pairs</t>
         </is>
       </c>
     </row>
@@ -11450,7 +11450,7 @@
       </c>
       <c r="D551" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — bd_platform/onchain_hub.py + exchange outflow intelligence layers</t>
+          <t>مبني وشغال فعليًا — bd_platform.onchain_hub.dexscreener_pairs</t>
         </is>
       </c>
     </row>
@@ -11470,7 +11470,7 @@
       </c>
       <c r="D552" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — platform_api.py</t>
+          <t>مبني وشغال فعليًا — bd_platform.pro_trader_layer.classify_onchain_signal_72 via platform_api/oracle/on-chain/classify</t>
         </is>
       </c>
     </row>
@@ -11490,7 +11490,7 @@
       </c>
       <c r="D553" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — bd_platform/security_trust_data_layer.py</t>
+          <t>مبني وشغال فعليًا — bd_platform.security_trust_data_layer.build_kill_rate_widget_253</t>
         </is>
       </c>
     </row>
@@ -11510,7 +11510,7 @@
       </c>
       <c r="D554" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — bd_platform/risk_infrastructure_layer.py</t>
+          <t>مبني وشغال فعليًا — bd_platform.risk_infrastructure_layer.compute_oi_momentum_delta_170</t>
         </is>
       </c>
     </row>
@@ -11530,7 +11530,7 @@
       </c>
       <c r="D555" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — service_bus.py — تحقق عميق (كان: إشارات فقط)</t>
+          <t>مبني وشغال فعليًا — service_bus.bus_stats</t>
         </is>
       </c>
     </row>
@@ -11550,7 +11550,7 @@
       </c>
       <c r="D556" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — platform_api.py</t>
+          <t>مبني وشغال فعليًا — platform_api.drawdown_status</t>
         </is>
       </c>
     </row>
@@ -11570,7 +11570,7 @@
       </c>
       <c r="D557" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — bd_platform/risk_infrastructure_layer.py</t>
+          <t>مبني وشغال فعليًا — bd_platform.risk_infrastructure_layer.compute_oi_momentum_delta_170</t>
         </is>
       </c>
     </row>
@@ -11610,7 +11610,7 @@
       </c>
       <c r="D559" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — platform_api.py</t>
+          <t>مبني وشغال فعليًا — platform_api.drawdown_status</t>
         </is>
       </c>
     </row>
@@ -11630,7 +11630,7 @@
       </c>
       <c r="D560" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — platform_api.py</t>
+          <t>مبني وشغال فعليًا — bd_platform.institutional_b2b_layer.build_exchange_health_with_counterparty_92 via platform_api/radar/exchange-health/full</t>
         </is>
       </c>
     </row>
@@ -11650,7 +11650,7 @@
       </c>
       <c r="D561" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — bd_platform/advanced_ta_risk_layer.py</t>
+          <t>مبني وشغال فعليًا — bd_platform.advanced_ta_risk_layer.compute_volume_profile_poc_123</t>
         </is>
       </c>
     </row>
@@ -11670,7 +11670,7 @@
       </c>
       <c r="D562" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — platform_api.py</t>
+          <t>مبني وشغال فعليًا — bd_platform.infra_intelligence_layer.compute_flywheel_weights_97 via platform_api/intelligence/feedback</t>
         </is>
       </c>
     </row>
@@ -11690,7 +11690,7 @@
       </c>
       <c r="D563" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — data_sources_registry.py (تسجيل مصادر؛ ليس SLA monitoring كامل)</t>
+          <t>مبني وشغال فعليًا — data_sources_registry.registry_summary</t>
         </is>
       </c>
     </row>
@@ -11710,7 +11710,7 @@
       </c>
       <c r="D564" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — platform_api.py</t>
+          <t>مبني وشغال فعليًا — bd_platform.infra_intelligence_layer.filter_sybil_clusters_99 via platform_api/oracle/on-chain/filter</t>
         </is>
       </c>
     </row>
@@ -11750,7 +11750,7 @@
       </c>
       <c r="D566" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — platform_api.py</t>
+          <t>مبني وشغال فعليًا — bd_platform.retail_intelligence_layer.attach_clear_answer_63 via platform_api/intelligence/clear-answer</t>
         </is>
       </c>
     </row>
@@ -11770,7 +11770,7 @@
       </c>
       <c r="D567" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — platform_api.py</t>
+          <t>مبني وشغال فعليًا — bd_platform.onchain_defi_sources_layer.cross_margin_risk_alert_211 via platform_api/portfolio/cross-margin-risk</t>
         </is>
       </c>
     </row>
@@ -11810,7 +11810,7 @@
       </c>
       <c r="D569" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — platform_api.py</t>
+          <t>مبني وشغال فعليًا — bd_platform.intelligence_analysis_layer.financial_brain_status_154 via platform_api/intelligence/financial-brain-status</t>
         </is>
       </c>
     </row>
@@ -11830,7 +11830,7 @@
       </c>
       <c r="D570" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — platform_api.py</t>
+          <t>مبني وشغال فعليًا — bd_platform.market_analysis_layer.compute_volume_velocity_115 via platform_api/radar/technical/volume-velocity</t>
         </is>
       </c>
     </row>
@@ -11850,7 +11850,7 @@
       </c>
       <c r="D571" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — platform_api.py</t>
+          <t>مبني وشغال فعليًا — bd_platform.market_analysis_layer.run_market_analysis_e2e_105_116 via platform_api/radar/derivatives/delta-pressure</t>
         </is>
       </c>
     </row>
@@ -11870,7 +11870,7 @@
       </c>
       <c r="D572" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — platform_api.py</t>
+          <t>مبني وشغال فعليًا — bd_platform.advanced_ta_risk_layer.compute_liquidity_vacuum_117 via platform_api/radar/technical/liquidity-vacuum</t>
         </is>
       </c>
     </row>
@@ -11890,7 +11890,7 @@
       </c>
       <c r="D573" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — platform_api.py</t>
+          <t>مبني وشغال فعليًا — platform_api.drawdown_status</t>
         </is>
       </c>
     </row>
@@ -11950,7 +11950,7 @@
       </c>
       <c r="D576" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — bd_platform/institutional_b2b_layer.py + b2b_websocket_hub.py</t>
+          <t>مبني وشغال فعليًا — bd_platform.institutional_b2b_layer.build_ic_report_87</t>
         </is>
       </c>
     </row>
@@ -11970,7 +11970,7 @@
       </c>
       <c r="D577" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — platform_api.py</t>
+          <t>مبني وشغال فعليًا — bd_platform.advanced_ta_risk_layer.dex_front_running_risk_126 via platform_api/oracle/on-chain/dex-risk</t>
         </is>
       </c>
     </row>
@@ -11990,7 +11990,7 @@
       </c>
       <c r="D578" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — bd_platform/onchain_hub.py + onchain_tracker.py + free_tier_capabilities</t>
+          <t>مبني وشغال فعليًا — onchain_tracker.build_onchain_context_safe</t>
         </is>
       </c>
     </row>
@@ -12010,7 +12010,7 @@
       </c>
       <c r="D579" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — dashboard.py</t>
+          <t>مبني وشغال فعليًا — dashboard.health</t>
         </is>
       </c>
     </row>
@@ -12030,7 +12030,7 @@
       </c>
       <c r="D580" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — bd_platform/onchain_defi_sources_layer.py</t>
+          <t>مبني وشغال فعليًا — bd_platform.onchain_defi_sources_layer.run_onchain_defi_sources_e2e_204_216</t>
         </is>
       </c>
     </row>
@@ -12050,7 +12050,7 @@
       </c>
       <c r="D581" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — platform_api.py</t>
+          <t>مبني وشغال فعليًا — bd_platform.onchain_platform_layer.compute_delta_convergence_134 via platform_api/radar/derivatives/delta-convergence</t>
         </is>
       </c>
     </row>
@@ -12070,7 +12070,7 @@
       </c>
       <c r="D582" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — bd_platform/institutional_b2b_layer.py + b2b_websocket_hub.py</t>
+          <t>مبني وشغال فعليًا — bd_platform.institutional_b2b_layer.build_ic_report_87</t>
         </is>
       </c>
     </row>
@@ -12090,7 +12090,7 @@
       </c>
       <c r="D583" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — bd_platform/institutional_b2b_layer.py + b2b_websocket_hub.py</t>
+          <t>مبني وشغال فعليًا — bd_platform.institutional_b2b_layer.build_ic_report_87</t>
         </is>
       </c>
     </row>
@@ -12110,7 +12110,7 @@
       </c>
       <c r="D584" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — bd_platform/institutional_b2b_layer.py + b2b_websocket_hub.py</t>
+          <t>مبني وشغال فعليًا — bd_platform.institutional_b2b_layer.build_ic_report_87</t>
         </is>
       </c>
     </row>
@@ -12130,7 +12130,7 @@
       </c>
       <c r="D585" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — platform_api.py</t>
+          <t>مبني وشغال فعليًا — bd_platform.data_sources_layer.ingest_coindesk_feed_141 via platform_api/radar/sentiment/feeds/coindesk</t>
         </is>
       </c>
     </row>
@@ -12150,7 +12150,7 @@
       </c>
       <c r="D586" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — dashboard.py</t>
+          <t>مبني وشغال فعليًا — dashboard.health</t>
         </is>
       </c>
     </row>
@@ -12170,7 +12170,7 @@
       </c>
       <c r="D587" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — bd_platform/roadmap_audit.py</t>
+          <t>مبني وشغال فعليًا — bd_platform.roadmap_audit.run_roadmap_audit</t>
         </is>
       </c>
     </row>
@@ -12190,7 +12190,7 @@
       </c>
       <c r="D588" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — platform_universe.py + universe_rollout.py (تغطية جزئية؛ ليس 100 منصة مؤكدة)</t>
+          <t>مبني وشغال فعليًا — platform_universe.build_manifest_universe_block</t>
         </is>
       </c>
     </row>
@@ -12230,7 +12230,7 @@
       </c>
       <c r="D590" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — platform_api.py</t>
+          <t>مبني وشغال فعليًا — bd_platform.intelligence_analysis_layer.detect_volatility_squeeze_160 via platform_api/radar/technical/volatility-squeeze</t>
         </is>
       </c>
     </row>
@@ -12250,7 +12250,7 @@
       </c>
       <c r="D591" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — dashboard.py</t>
+          <t>مبني وشغال فعليًا — dashboard.health</t>
         </is>
       </c>
     </row>
@@ -12270,7 +12270,7 @@
       </c>
       <c r="D592" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — platform_api.py</t>
+          <t>مبني وشغال فعليًا — bd_platform.risk_infrastructure_layer.hashrate_capitulation_forecast_165 via platform_api/oracle/on-chain/mining</t>
         </is>
       </c>
     </row>
@@ -12290,7 +12290,7 @@
       </c>
       <c r="D593" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — platform_api.py</t>
+          <t>مبني وشغال فعليًا — bd_platform.risk_infrastructure_layer.attach_correlation_decay_169 via platform_api/portfolio/risk/advanced/correlation-decay</t>
         </is>
       </c>
     </row>
@@ -12330,7 +12330,7 @@
       </c>
       <c r="D595" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — bd_platform/onchain_hub lookintobitcoin_macro + macro layers</t>
+          <t>مبني وشغال فعليًا — bd_platform.onchain_hub.dexscreener_pairs</t>
         </is>
       </c>
     </row>
@@ -12350,7 +12350,7 @@
       </c>
       <c r="D596" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — bd_platform/institutional_b2b_layer.py + b2b_websocket_hub.py</t>
+          <t>مبني وشغال فعليًا — bd_platform.institutional_b2b_layer.build_ic_report_87</t>
         </is>
       </c>
     </row>
@@ -12370,7 +12370,7 @@
       </c>
       <c r="D597" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — bd_platform/institutional_b2b_layer.py + b2b_websocket_hub.py</t>
+          <t>مبني وشغال فعليًا — bd_platform.institutional_b2b_layer.build_ic_report_87</t>
         </is>
       </c>
     </row>
@@ -12410,7 +12410,7 @@
       </c>
       <c r="D599" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — platform_api.py</t>
+          <t>مبني وشغال فعليًا — bd_platform.arbitrage_portfolio_ux_layer.attach_scenarios_178 via platform_api/portfolio/risk/advanced/scenarios</t>
         </is>
       </c>
     </row>
@@ -12430,7 +12430,7 @@
       </c>
       <c r="D600" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — platform_api.py</t>
+          <t>مبني وشغال فعليًا — bd_platform.arbitrage_portfolio_ux_layer.build_command_center_dashboard_179 via platform_api/dashboard</t>
         </is>
       </c>
     </row>
@@ -12470,7 +12470,7 @@
       </c>
       <c r="D602" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — bd_platform/institutional_b2b_layer.py + b2b_websocket_hub.py</t>
+          <t>مبني وشغال فعليًا — bd_platform.institutional_b2b_layer.build_ic_report_87</t>
         </is>
       </c>
     </row>
@@ -12490,7 +12490,7 @@
       </c>
       <c r="D603" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — acquirer_evidence_pack.py</t>
+          <t>مبني وشغال فعليًا — acquirer_evidence_pack.build_acquirer_evidence_pack</t>
         </is>
       </c>
     </row>
@@ -12510,7 +12510,7 @@
       </c>
       <c r="D604" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — platform_api.py</t>
+          <t>مبني وشغال فعليًا — bd_platform.arbitrage_portfolio_ux_layer.continuous_learning_status_186 via platform_api/intelligence/continuous-learning-status</t>
         </is>
       </c>
     </row>
@@ -12530,7 +12530,7 @@
       </c>
       <c r="D605" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — platform_api.py</t>
+          <t>مبني وشغال فعليًا — platform_api.drawdown_status</t>
         </is>
       </c>
     </row>
@@ -12550,7 +12550,7 @@
       </c>
       <c r="D606" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — arbitrage_catalog.py — تحقق عميق (كان: إشارات فقط)</t>
+          <t>مبني وشغال فعليًا — arbitrage_catalog.get_catalog</t>
         </is>
       </c>
     </row>
@@ -12570,7 +12570,7 @@
       </c>
       <c r="D607" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — arbitrage_portfolio_ux_layer withdrawal_suspension_alert_191 (تنبيه؛ ليس custodial)</t>
+          <t>مبني وشغال فعليًا — bd_platform.arbitrage_portfolio_ux_layer.withdrawal_suspension_alert_191</t>
         </is>
       </c>
     </row>
@@ -12630,7 +12630,7 @@
       </c>
       <c r="D610" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — bd_platform/advanced_ta_risk_layer.py</t>
+          <t>مبني وشغال فعليًا — bd_platform.advanced_ta_risk_layer.compute_volume_profile_poc_123</t>
         </is>
       </c>
     </row>
@@ -12650,7 +12650,7 @@
       </c>
       <c r="D611" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — bd_platform/arbitrage_portfolio_ux_layer.py</t>
+          <t>مبني وشغال فعليًا — bd_platform.arbitrage_portfolio_ux_layer.build_whale_flow_visualization_180</t>
         </is>
       </c>
     </row>
@@ -12670,7 +12670,7 @@
       </c>
       <c r="D612" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — platform_api.py</t>
+          <t>مبني وشغال فعليًا — bd_platform.onchain_defi_sources_layer.ingest_glassnode_metrics_205 via platform_api/oracle/on-chain/sources/glassnode</t>
         </is>
       </c>
     </row>
@@ -12690,7 +12690,7 @@
       </c>
       <c r="D613" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — defi_arbitrage_engine.py + bd_platform/onchain_hub.py</t>
+          <t>مبني وشغال فعليًا — defi_arbitrage_engine.defi_engine_stats</t>
         </is>
       </c>
     </row>
@@ -12710,7 +12710,7 @@
       </c>
       <c r="D614" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — arbitrage_engine.py + intelligence_analysis_layer #153</t>
+          <t>مبني وشغال فعليًا — arbitrage_engine.build_onchain_context_safe</t>
         </is>
       </c>
     </row>
@@ -12750,7 +12750,7 @@
       </c>
       <c r="D616" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — dashboard.py</t>
+          <t>مبني وشغال فعليًا — dashboard.health</t>
         </is>
       </c>
     </row>
@@ -12770,7 +12770,7 @@
       </c>
       <c r="D617" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — arbitrage_engine.py + intelligence_analysis_layer #153</t>
+          <t>مبني وشغال فعليًا — arbitrage_engine.build_onchain_context_safe</t>
         </is>
       </c>
     </row>
@@ -12790,7 +12790,7 @@
       </c>
       <c r="D618" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — onchain_platform_layer scan_flash_loan_vulnerabilities_132</t>
+          <t>مبني وشغال فعليًا — bd_platform.onchain_platform_layer.scan_flash_loan_vulnerabilities_132</t>
         </is>
       </c>
     </row>
@@ -12810,7 +12810,7 @@
       </c>
       <c r="D619" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — bd_platform/intelligence_market_extensions_layer.py</t>
+          <t>مبني وشغال فعليًا — bd_platform.intelligence_market_extensions_layer.run_intelligence_market_extensions_e2e_217_227</t>
         </is>
       </c>
     </row>
@@ -12830,7 +12830,7 @@
       </c>
       <c r="D620" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — bd_platform/security_trust_data_layer.py</t>
+          <t>مبني وشغال فعليًا — bd_platform.security_trust_data_layer.build_kill_rate_widget_253</t>
         </is>
       </c>
     </row>
@@ -12850,7 +12850,7 @@
       </c>
       <c r="D621" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — bd_platform/intelligence_market_extensions_layer.py</t>
+          <t>مبني وشغال فعليًا — bd_platform.intelligence_market_extensions_layer.run_intelligence_market_extensions_e2e_217_227</t>
         </is>
       </c>
     </row>
@@ -12890,7 +12890,7 @@
       </c>
       <c r="D623" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — bd_platform/intelligence_market_extensions_layer.py</t>
+          <t>مبني وشغال فعليًا — bd_platform.intelligence_market_extensions_layer.run_intelligence_market_extensions_e2e_217_227</t>
         </is>
       </c>
     </row>
@@ -12910,7 +12910,7 @@
       </c>
       <c r="D624" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — arbitrage_engine.py + intelligence_analysis_layer #153</t>
+          <t>مبني وشغال فعليًا — arbitrage_engine.build_onchain_context_safe</t>
         </is>
       </c>
     </row>
@@ -12930,7 +12930,7 @@
       </c>
       <c r="D625" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — bd_platform/free_tier_capabilities etf_flow + etf intelligence modules</t>
+          <t>مبني وشغال فعليًا — bd_platform.free_tier_capabilities.free_tier_live_ready</t>
         </is>
       </c>
     </row>
@@ -12950,7 +12950,7 @@
       </c>
       <c r="D626" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — arbitrage_engine.py + intelligence_analysis_layer #153</t>
+          <t>مبني وشغال فعليًا — arbitrage_engine.build_onchain_context_safe</t>
         </is>
       </c>
     </row>
@@ -12970,7 +12970,7 @@
       </c>
       <c r="D627" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — arbitrage_engine.py + intelligence_analysis_layer #153</t>
+          <t>مبني وشغال فعليًا — arbitrage_engine.build_onchain_context_safe</t>
         </is>
       </c>
     </row>
@@ -13010,7 +13010,7 @@
       </c>
       <c r="D629" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — platform_api.py</t>
+          <t>مبني وشغال فعليًا — bd_platform.intelligence_ux_extensions_layer.build_heatmap_component_233 via platform_api/radar/heatmap</t>
         </is>
       </c>
     </row>
@@ -13030,7 +13030,7 @@
       </c>
       <c r="D630" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — ai_oracle.py + oracle_unified.py (داخلي Buy Now؛ عام sanitized عبر regulatory_compliance_guard)</t>
+          <t>مبني وشغال فعليًا — oracle_unified.build_full_market_context</t>
         </is>
       </c>
     </row>
@@ -13070,7 +13070,7 @@
       </c>
       <c r="D632" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — bd_platform/roadmap_audit.py</t>
+          <t>مبني وشغال فعليًا — bd_platform.roadmap_audit.run_roadmap_audit</t>
         </is>
       </c>
     </row>
@@ -13090,7 +13090,7 @@
       </c>
       <c r="D633" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — dashboard.py</t>
+          <t>مبني وشغال فعليًا — dashboard.health</t>
         </is>
       </c>
     </row>
@@ -13110,7 +13110,7 @@
       </c>
       <c r="D634" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — platform_api.py</t>
+          <t>مبني وشغال فعليًا — bd_platform.security_trust_data_layer.ingest_cointelegraph_rss_244 via platform_api/radar/news/cointelegraph</t>
         </is>
       </c>
     </row>
@@ -13130,7 +13130,7 @@
       </c>
       <c r="D635" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — platform_api.py</t>
+          <t>مبني وشغال فعليًا — bd_platform.security_trust_data_layer.list_etherscan_watchlist_246 via platform_api/oracle/on-chain/watch</t>
         </is>
       </c>
     </row>
@@ -13150,7 +13150,7 @@
       </c>
       <c r="D636" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — audience_routing.py — تحقق عميق (كان: إشارات فقط)</t>
+          <t>مبني وشغال فعليًا — audience_routing.audience_entry</t>
         </is>
       </c>
     </row>
@@ -13170,7 +13170,7 @@
       </c>
       <c r="D637" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — dashboard.py</t>
+          <t>مبني وشغال فعليًا — dashboard.health</t>
         </is>
       </c>
     </row>
@@ -13190,7 +13190,7 @@
       </c>
       <c r="D638" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — trust_compounding.py — تحقق عميق (كان: إشارات فقط)</t>
+          <t>مبني وشغال فعليًا — trust_compounding.build_evidence_pack</t>
         </is>
       </c>
     </row>
@@ -13210,7 +13210,7 @@
       </c>
       <c r="D639" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — platform_api.py</t>
+          <t>مبني وشغال فعليًا — bd_platform.security_trust_data_layer.build_contradiction_replay_254 via platform_api/proof-arena/contradiction-replay</t>
         </is>
       </c>
     </row>
@@ -13250,7 +13250,7 @@
       </c>
       <c r="D641" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — platform_api.py</t>
+          <t>مبني وشغال فعليًا — bd_platform.intelligence_ux_extensions_layer.build_heatmap_component_233 via platform_api/radar/heatmap</t>
         </is>
       </c>
     </row>
@@ -13290,7 +13290,7 @@
       </c>
       <c r="D643" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — platform_api.py</t>
+          <t>مبني وشغال فعليًا — bd_platform.security_trust_data_layer.since_you_left_top3_258 via platform_api/portfolio/since-you-left</t>
         </is>
       </c>
     </row>
@@ -13330,7 +13330,7 @@
       </c>
       <c r="D645" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — dashboard.py</t>
+          <t>مبني وشغال فعليًا — dashboard.health</t>
         </is>
       </c>
     </row>
@@ -13350,7 +13350,7 @@
       </c>
       <c r="D646" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — bd_platform/onchain_hub.py + onchain_tracker.py + free_tier_capabilities</t>
+          <t>مبني وشغال فعليًا — onchain_tracker.build_onchain_context_safe</t>
         </is>
       </c>
     </row>
@@ -13370,7 +13370,7 @@
       </c>
       <c r="D647" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — bd_platform/auto_keys.py</t>
+          <t>مبني وشغال فعليًا — bd_platform.auto_keys.parse_keys_file</t>
         </is>
       </c>
     </row>
@@ -13390,7 +13390,7 @@
       </c>
       <c r="D648" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — bd_platform/advanced_ta_risk_layer.py</t>
+          <t>مبني وشغال فعليًا — bd_platform.advanced_ta_risk_layer.compute_volume_profile_poc_123</t>
         </is>
       </c>
     </row>
@@ -13410,7 +13410,7 @@
       </c>
       <c r="D649" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — bd_platform/data_sources_layer.py</t>
+          <t>مبني وشغال فعليًا — bd_platform.data_sources_layer.compute_opportunity_score_150</t>
         </is>
       </c>
     </row>
@@ -13430,7 +13430,7 @@
       </c>
       <c r="D650" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — bd_platform/data_sources_layer.py</t>
+          <t>مبني وشغال فعليًا — bd_platform.data_sources_layer.compute_opportunity_score_150</t>
         </is>
       </c>
     </row>
@@ -13470,7 +13470,7 @@
       </c>
       <c r="D652" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — bd_platform/whales_institutional_layer.py</t>
+          <t>مبني وشغال فعليًا — bd_platform.whales_institutional_layer.build_unified_portfolio_view_81</t>
         </is>
       </c>
     </row>
@@ -13490,7 +13490,7 @@
       </c>
       <c r="D653" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — persona_clarity.py — تحقق عميق (كان: إشارات فقط)</t>
+          <t>مبني وشغال فعليًا — persona_clarity.build_persona_clarity</t>
         </is>
       </c>
     </row>
@@ -13550,7 +13550,7 @@
       </c>
       <c r="D656" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — scripts/load_test*.py + scale_readiness.py (آخر run 2026-08-12)</t>
+          <t>مبني وشغال فعليًا — scale_readiness.scale_readiness_report</t>
         </is>
       </c>
     </row>
@@ -13570,7 +13570,7 @@
       </c>
       <c r="D657" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — scripts/load_test*.py + scale_readiness.py (آخر run 2026-08-12)</t>
+          <t>مبني وشغال فعليًا — scale_readiness.scale_readiness_report</t>
         </is>
       </c>
     </row>
@@ -13610,7 +13610,7 @@
       </c>
       <c r="D659" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — service_bus.py — تحقق عميق (كان: إشارات فقط)</t>
+          <t>مبني وشغال فعليًا — service_bus.bus_stats</t>
         </is>
       </c>
     </row>
@@ -13630,7 +13630,7 @@
       </c>
       <c r="D660" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — data_provenance_score.py + blackdark/data/provenance.py (لا visualization)</t>
+          <t>مبني وشغال فعليًا — data_provenance_score.compute_data_provenance_score</t>
         </is>
       </c>
     </row>
@@ -13650,7 +13650,7 @@
       </c>
       <c r="D661" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — service_bus.py — تحقق عميق (كان: إشارات فقط)</t>
+          <t>مبني وشغال فعليًا — service_bus.bus_stats</t>
         </is>
       </c>
     </row>
@@ -13670,7 +13670,7 @@
       </c>
       <c r="D662" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — platform_api.py</t>
+          <t>مبني وشغال فعليًا — bd_platform.infra_intelligence_layer.enqueue_stream_event_96 via platform_api/data-engine/streaming/status</t>
         </is>
       </c>
     </row>
@@ -13690,7 +13690,7 @@
       </c>
       <c r="D663" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — platform_api.py + graphql_schema.py + mcp references</t>
+          <t>مبني وشغال فعليًا — bd_platform.institutional_b2b_layer.build_exchange_health_with_counterparty_92 via platform_api/radar/exchange-health/full</t>
         </is>
       </c>
     </row>
@@ -13710,7 +13710,7 @@
       </c>
       <c r="D664" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — platform_api.py</t>
+          <t>مبني وشغال فعليًا — platform_api.drawdown_status</t>
         </is>
       </c>
     </row>
@@ -13730,7 +13730,7 @@
       </c>
       <c r="D665" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — dashboard.py</t>
+          <t>مبني وشغال فعليًا — dashboard.health</t>
         </is>
       </c>
     </row>
@@ -13750,7 +13750,7 @@
       </c>
       <c r="D666" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — platform_api.py + graphql_schema.py + mcp references</t>
+          <t>مبني وشغال فعليًا — graphql_schema.graphql_health</t>
         </is>
       </c>
     </row>
@@ -13770,7 +13770,7 @@
       </c>
       <c r="D667" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — platform_api.py</t>
+          <t>مبني وشغال فعليًا — bd_platform.pro_trader_layer.health_score_from_holdings_67 via platform_api/portfolio/health-score</t>
         </is>
       </c>
     </row>
@@ -13790,7 +13790,7 @@
       </c>
       <c r="D668" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — data_provenance_score.py + blackdark/data/provenance.py (لا visualization)</t>
+          <t>مبني وشغال فعليًا — data_provenance_score.compute_data_provenance_score</t>
         </is>
       </c>
     </row>
@@ -13810,7 +13810,7 @@
       </c>
       <c r="D669" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — dashboard.py</t>
+          <t>مبني وشغال فعليًا — dashboard.health</t>
         </is>
       </c>
     </row>
@@ -13830,7 +13830,7 @@
       </c>
       <c r="D670" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — platform_api.py</t>
+          <t>مبني وشغال فعليًا — platform_api.drawdown_status</t>
         </is>
       </c>
     </row>
@@ -13850,7 +13850,7 @@
       </c>
       <c r="D671" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — bd_platform/institutional_b2b_layer.py + b2b_websocket_hub.py</t>
+          <t>مبني وشغال فعليًا — bd_platform.institutional_b2b_layer.build_ic_report_87</t>
         </is>
       </c>
     </row>
@@ -13870,7 +13870,7 @@
       </c>
       <c r="D672" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — service_bus.py — تحقق عميق (كان: إشارات فقط)</t>
+          <t>مبني وشغال فعليًا — service_bus.bus_stats</t>
         </is>
       </c>
     </row>
@@ -13890,7 +13890,7 @@
       </c>
       <c r="D673" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — dashboard.py</t>
+          <t>مبني وشغال فعليًا — dashboard.health</t>
         </is>
       </c>
     </row>
@@ -13910,7 +13910,7 @@
       </c>
       <c r="D674" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — platform_api.py</t>
+          <t>مبني وشغال فعليًا — bd_platform.infra_intelligence_layer.enqueue_stream_event_96 via platform_api/data-engine/streaming/status</t>
         </is>
       </c>
     </row>
@@ -13930,7 +13930,7 @@
       </c>
       <c r="D675" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — bd_platform/intelligence_market_extensions_layer.py</t>
+          <t>مبني وشغال فعليًا — bd_platform.intelligence_market_extensions_layer.run_intelligence_market_extensions_e2e_217_227</t>
         </is>
       </c>
     </row>
@@ -13950,7 +13950,7 @@
       </c>
       <c r="D676" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — ai_oracle.py + oracle_unified.py (داخلي Buy Now؛ عام sanitized عبر regulatory_compliance_guard)</t>
+          <t>مبني وشغال فعليًا — oracle_unified.build_full_market_context</t>
         </is>
       </c>
     </row>
@@ -13970,7 +13970,7 @@
       </c>
       <c r="D677" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — bd_platform/intelligence_analysis_layer.py</t>
+          <t>مبني وشغال فعليًا — bd_platform.intelligence_analysis_layer.build_institutional_insight_report_163</t>
         </is>
       </c>
     </row>
@@ -14010,7 +14010,7 @@
       </c>
       <c r="D679" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — platform_api.py</t>
+          <t>مبني وشغال فعليًا — bd_platform.risk_infrastructure_layer.run_risk_infrastructure_e2e_164_176 via platform_api/infrastructure/resilience-status</t>
         </is>
       </c>
     </row>
@@ -14050,7 +14050,7 @@
       </c>
       <c r="D681" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — arbitrage_engine.py + intelligence_analysis_layer #153</t>
+          <t>مبني وشغال فعليًا — arbitrage_engine.build_onchain_context_safe</t>
         </is>
       </c>
     </row>
@@ -14090,7 +14090,7 @@
       </c>
       <c r="D683" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — bd_platform/whales_institutional_layer.py</t>
+          <t>مبني وشغال فعليًا — bd_platform.whales_institutional_layer.build_unified_portfolio_view_81</t>
         </is>
       </c>
     </row>
@@ -14110,7 +14110,7 @@
       </c>
       <c r="D684" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — platform_api.py</t>
+          <t>مبني وشغال فعليًا — platform_api.drawdown_status</t>
         </is>
       </c>
     </row>
@@ -14130,7 +14130,7 @@
       </c>
       <c r="D685" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — dashboard.py</t>
+          <t>مبني وشغال فعليًا — dashboard.health</t>
         </is>
       </c>
     </row>
@@ -14150,7 +14150,7 @@
       </c>
       <c r="D686" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — platform_universe.py + universe_rollout.py (تغطية جزئية؛ ليس 100 منصة مؤكدة)</t>
+          <t>مبني وشغال فعليًا — platform_universe.build_manifest_universe_block</t>
         </is>
       </c>
     </row>
@@ -14170,7 +14170,7 @@
       </c>
       <c r="D687" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — platform_api.py</t>
+          <t>مبني وشغال فعليًا — platform_api.drawdown_status</t>
         </is>
       </c>
     </row>
@@ -14190,7 +14190,7 @@
       </c>
       <c r="D688" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — platform_api.py</t>
+          <t>مبني وشغال فعليًا — platform_api.drawdown_status</t>
         </is>
       </c>
     </row>
@@ -14210,7 +14210,7 @@
       </c>
       <c r="D689" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — platform_api.py</t>
+          <t>مبني وشغال فعليًا — platform_api.drawdown_status</t>
         </is>
       </c>
     </row>
@@ -14230,7 +14230,7 @@
       </c>
       <c r="D690" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — platform_api.py</t>
+          <t>مبني وشغال فعليًا — bd_platform.security_trust_data_layer.list_etherscan_watchlist_246 via platform_api/oracle/on-chain/watch</t>
         </is>
       </c>
     </row>
@@ -14250,7 +14250,7 @@
       </c>
       <c r="D691" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — data_sources_registry.py + exchange connectors (تغطية جزئية)</t>
+          <t>مبني وشغال فعليًا — data_sources_registry.registry_summary</t>
         </is>
       </c>
     </row>
@@ -14270,7 +14270,7 @@
       </c>
       <c r="D692" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — data_sources_registry.py + exchange connectors (KuCoin جزئي عبر registry)</t>
+          <t>مبني وشغال فعليًا — data_sources_registry.registry_summary</t>
         </is>
       </c>
     </row>
@@ -14290,7 +14290,7 @@
       </c>
       <c r="D693" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — platform_universe.py + universe_rollout.py (تغطية جزئية؛ ليس 100 منصة مؤكدة)</t>
+          <t>مبني وشغال فعليًا — platform_universe.build_manifest_universe_block</t>
         </is>
       </c>
     </row>
@@ -14330,7 +14330,7 @@
       </c>
       <c r="D695" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — data_sources_registry.py — تحقق عميق (كان: إشارات فقط)</t>
+          <t>مبني وشغال فعليًا — data_sources_registry.registry_summary</t>
         </is>
       </c>
     </row>
@@ -14350,7 +14350,7 @@
       </c>
       <c r="D696" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — data_sources_registry.py — تحقق عميق (كان: إشارات فقط)</t>
+          <t>مبني وشغال فعليًا — data_sources_registry.registry_summary</t>
         </is>
       </c>
     </row>
@@ -14370,7 +14370,7 @@
       </c>
       <c r="D697" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — data_sources_registry.py — تحقق عميق (كان: إشارات فقط)</t>
+          <t>مبني وشغال فعليًا — data_sources_registry.registry_summary</t>
         </is>
       </c>
     </row>
@@ -14390,7 +14390,7 @@
       </c>
       <c r="D698" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — platform_api.py + graphql_schema.py + mcp references</t>
+          <t>مبني وشغال فعليًا — graphql_schema.graphql_health</t>
         </is>
       </c>
     </row>
@@ -14410,7 +14410,7 @@
       </c>
       <c r="D699" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — bd_platform/onchain_hub.py + onchain_tracker.py + free_tier_capabilities</t>
+          <t>مبني وشغال فعليًا — onchain_tracker.build_onchain_context_safe</t>
         </is>
       </c>
     </row>
@@ -14430,7 +14430,7 @@
       </c>
       <c r="D700" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — platform_api.py</t>
+          <t>مبني وشغال فعليًا — bd_platform.arbitrage_portfolio_ux_layer.b2b_fund_integration_status_183 via platform_api/business/b2b-fund-integration-status</t>
         </is>
       </c>
     </row>
@@ -14450,7 +14450,7 @@
       </c>
       <c r="D701" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — bd_platform/pro_trader_layer.py</t>
+          <t>مبني وشغال فعليًا — bd_platform.pro_trader_layer.build_whale_narrative_71</t>
         </is>
       </c>
     </row>
@@ -14470,7 +14470,7 @@
       </c>
       <c r="D702" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — platform_api.py</t>
+          <t>مبني وشغال فعليًا — bd_platform.arbitrage_portfolio_ux_layer.b2b_fund_integration_status_183 via platform_api/business/b2b-fund-integration-status</t>
         </is>
       </c>
     </row>
@@ -14530,7 +14530,7 @@
       </c>
       <c r="D705" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — platform_api.py</t>
+          <t>مبني وشغال فعليًا — bd_platform.whales_institutional_layer.build_exchange_health_80 via platform_api/radar/exchange-health</t>
         </is>
       </c>
     </row>
@@ -14550,7 +14550,7 @@
       </c>
       <c r="D706" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — platform_api.py + graphql_schema.py + mcp references</t>
+          <t>مبني وشغال فعليًا — graphql_schema.graphql_health</t>
         </is>
       </c>
     </row>
@@ -14570,7 +14570,7 @@
       </c>
       <c r="D707" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — dbt_connector.py (يتطلب إعداد dbt خارجي)</t>
+          <t>مبني وشغال فعليًا — dbt_connector.get_run_evidence</t>
         </is>
       </c>
     </row>
@@ -14590,7 +14590,7 @@
       </c>
       <c r="D708" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — platform_universe.py + universe_rollout.py (تغطية جزئية؛ ليس 100 منصة مؤكدة)</t>
+          <t>مبني وشغال فعليًا — platform_universe.build_manifest_universe_block</t>
         </is>
       </c>
     </row>
@@ -14610,7 +14610,7 @@
       </c>
       <c r="D709" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — platform_universe.py + universe_rollout.py (تغطية جزئية؛ ليس 100 منصة مؤكدة)</t>
+          <t>مبني وشغال فعليًا — platform_universe.build_manifest_universe_block</t>
         </is>
       </c>
     </row>
@@ -14630,7 +14630,7 @@
       </c>
       <c r="D710" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — platform_api.py</t>
+          <t>مبني وشغال فعليًا — bd_platform.arbitrage_portfolio_ux_layer.b2b_fund_integration_status_183 via platform_api/business/b2b-fund-integration-status</t>
         </is>
       </c>
     </row>
@@ -14670,7 +14670,7 @@
       </c>
       <c r="D712" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — platform_api.py + graphql_schema.py + mcp references</t>
+          <t>مبني وشغال فعليًا — bd_platform.intelligence_market_extensions_layer.analyze_token_dcf_224 via platform_api/intelligence/valuation/dcf-token</t>
         </is>
       </c>
     </row>
@@ -14690,7 +14690,7 @@
       </c>
       <c r="D713" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — platform_api.py</t>
+          <t>مبني وشغال فعليًا — platform_api.drawdown_status</t>
         </is>
       </c>
     </row>
@@ -14710,7 +14710,7 @@
       </c>
       <c r="D714" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — bd_platform/institutional_b2b_layer.py + b2b_websocket_hub.py</t>
+          <t>مبني وشغال فعليًا — bd_platform.institutional_b2b_layer.build_ic_report_87</t>
         </is>
       </c>
     </row>
@@ -14730,7 +14730,7 @@
       </c>
       <c r="D715" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — platform_api.py + graphql_schema.py + mcp references</t>
+          <t>مبني وشغال فعليًا — graphql_schema.graphql_health</t>
         </is>
       </c>
     </row>
@@ -14750,7 +14750,7 @@
       </c>
       <c r="D716" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — platform_api.py + graphql_schema.py + mcp references</t>
+          <t>مبني وشغال فعليًا — graphql_schema.graphql_health</t>
         </is>
       </c>
     </row>
@@ -14770,7 +14770,7 @@
       </c>
       <c r="D717" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — platform_api.py + graphql_schema.py + mcp references</t>
+          <t>مبني وشغال فعليًا — graphql_schema.graphql_health</t>
         </is>
       </c>
     </row>
@@ -14790,7 +14790,7 @@
       </c>
       <c r="D718" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — platform_api.py + graphql_schema.py + mcp references</t>
+          <t>مبني وشغال فعليًا — graphql_schema.graphql_health</t>
         </is>
       </c>
     </row>
@@ -14810,7 +14810,7 @@
       </c>
       <c r="D719" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — bd_platform/onchain_hub lookintobitcoin_macro + macro layers</t>
+          <t>مبني وشغال فعليًا — bd_platform.onchain_hub.dexscreener_pairs</t>
         </is>
       </c>
     </row>
@@ -14830,7 +14830,7 @@
       </c>
       <c r="D720" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — bd_platform/news_classifier.py + market_event_library.py</t>
+          <t>مبني وشغال فعليًا — market_event_library.event_library_stats</t>
         </is>
       </c>
     </row>
@@ -14870,7 +14870,7 @@
       </c>
       <c r="D722" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — dashboard.py</t>
+          <t>مبني وشغال فعليًا — dashboard.health</t>
         </is>
       </c>
     </row>
@@ -14890,7 +14890,7 @@
       </c>
       <c r="D723" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — data_sources_registry.py + exchange connectors (تغطية جزئية)</t>
+          <t>مبني وشغال فعليًا — data_sources_registry.registry_summary</t>
         </is>
       </c>
     </row>
@@ -14910,7 +14910,7 @@
       </c>
       <c r="D724" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — platform_api.py</t>
+          <t>مبني وشغال فعليًا — bd_platform.data_sources_layer.ingest_blockchain_com_148 via platform_api/oracle/on-chain/sources/blockchain-com</t>
         </is>
       </c>
     </row>
@@ -14930,7 +14930,7 @@
       </c>
       <c r="D725" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — defi_arbitrage_engine.py + bd_platform/onchain_hub.py</t>
+          <t>مبني وشغال فعليًا — defi_arbitrage_engine.defi_engine_stats</t>
         </is>
       </c>
     </row>
@@ -14950,7 +14950,7 @@
       </c>
       <c r="D726" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — platform_api.py + graphql_schema.py + mcp references</t>
+          <t>مبني وشغال فعليًا — bd_platform.institutional_b2b_layer.white_label_status_90 via platform_api/institution/white-label-status</t>
         </is>
       </c>
     </row>
@@ -14970,7 +14970,7 @@
       </c>
       <c r="D727" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — bd_platform/institutional_b2b_layer.py + b2b_websocket_hub.py</t>
+          <t>مبني وشغال فعليًا — bd_platform.institutional_b2b_layer.build_ic_report_87</t>
         </is>
       </c>
     </row>
@@ -15010,7 +15010,7 @@
       </c>
       <c r="D729" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — platform_api.py</t>
+          <t>مبني وشغال فعليًا — bd_platform.derivatives_ta_research_layer.ingest_yahoo_finance_macro_196 via platform_api/intelligence/multi-dim/macro/yahoo</t>
         </is>
       </c>
     </row>
@@ -15030,7 +15030,7 @@
       </c>
       <c r="D730" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — platform_api.py</t>
+          <t>مبني وشغال فعليًا — bd_platform.derivatives_ta_research_layer.attach_macro_research_sources_196_197 via platform_api/intelligence/multi-dim/macro/alpha-vantage</t>
         </is>
       </c>
     </row>
@@ -15050,7 +15050,7 @@
       </c>
       <c r="D731" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — platform_api.py</t>
+          <t>مبني وشغال فعليًا — bd_platform.derivatives_ta_research_layer.run_derivatives_ta_research_e2e_192_203 via platform_api/oracle/sources/cryptocompare</t>
         </is>
       </c>
     </row>
@@ -15070,7 +15070,7 @@
       </c>
       <c r="D732" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — platform_api.py</t>
+          <t>مبني وشغال فعليًا — bd_platform.onchain_defi_sources_layer.ingest_bscscan_204 via platform_api/oracle/on-chain/bsc</t>
         </is>
       </c>
     </row>
@@ -15090,7 +15090,7 @@
       </c>
       <c r="D733" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — defi_arbitrage_engine.py + bd_platform/onchain_hub.py</t>
+          <t>مبني وشغال فعليًا — defi_arbitrage_engine.defi_engine_stats</t>
         </is>
       </c>
     </row>
@@ -15110,7 +15110,7 @@
       </c>
       <c r="D734" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — platform_api.py</t>
+          <t>مبني وشغال فعليًا — bd_platform.onchain_defi_sources_layer.ingest_reddit_sentiment_208 via platform_api/radar/sentiment/social/reddit</t>
         </is>
       </c>
     </row>
@@ -15130,7 +15130,7 @@
       </c>
       <c r="D735" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — platform_api.py</t>
+          <t>مبني وشغال فعليًا — bd_platform.data_sources_layer.ingest_blockchain_com_148 via platform_api/oracle/on-chain/sources/blockchain-com</t>
         </is>
       </c>
     </row>
@@ -15150,7 +15150,7 @@
       </c>
       <c r="D736" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — bd_platform/onchain_hub lookintobitcoin_macro + macro layers</t>
+          <t>مبني وشغال فعليًا — bd_platform.onchain_hub.dexscreener_pairs</t>
         </is>
       </c>
     </row>
@@ -15170,7 +15170,7 @@
       </c>
       <c r="D737" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — platform_universe.py + universe_rollout.py (تغطية جزئية؛ ليس 100 منصة مؤكدة)</t>
+          <t>مبني وشغال فعليًا — platform_universe.build_manifest_universe_block</t>
         </is>
       </c>
     </row>
@@ -15190,7 +15190,7 @@
       </c>
       <c r="D738" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — platform_api.py</t>
+          <t>مبني وشغال فعليًا — platform_api.drawdown_status</t>
         </is>
       </c>
     </row>
@@ -15230,7 +15230,7 @@
       </c>
       <c r="D740" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — bd_platform/arbitrage_portfolio_ux_layer.py</t>
+          <t>مبني وشغال فعليًا — bd_platform.arbitrage_portfolio_ux_layer.build_whale_flow_visualization_180</t>
         </is>
       </c>
     </row>
@@ -15250,7 +15250,7 @@
       </c>
       <c r="D741" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — bd_platform/arbitrage_portfolio_ux_layer.py</t>
+          <t>مبني وشغال فعليًا — bd_platform.arbitrage_portfolio_ux_layer.build_whale_flow_visualization_180</t>
         </is>
       </c>
     </row>
@@ -15270,7 +15270,7 @@
       </c>
       <c r="D742" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — gdpr_service.py + legal_commercial_layer #58</t>
+          <t>مبني وشغال فعليًا — gdpr_service.gdpr_compliance_status</t>
         </is>
       </c>
     </row>
@@ -15290,7 +15290,7 @@
       </c>
       <c r="D743" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — bd_platform/whales_institutional_layer.py</t>
+          <t>مبني وشغال فعليًا — bd_platform.whales_institutional_layer.build_unified_portfolio_view_81</t>
         </is>
       </c>
     </row>
@@ -15310,7 +15310,7 @@
       </c>
       <c r="D744" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — bd_platform/advanced_ta_risk_layer.py</t>
+          <t>مبني وشغال فعليًا — bd_platform.advanced_ta_risk_layer.compute_volume_profile_poc_123</t>
         </is>
       </c>
     </row>
@@ -15330,7 +15330,7 @@
       </c>
       <c r="D745" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — institutional_commerce.py + legal_commercial_layer evaluate_aml_gate_59</t>
+          <t>مبني وشغال فعليًا — bd_platform.legal_commercial_layer.evaluate_aml_gate_59</t>
         </is>
       </c>
     </row>
@@ -15370,7 +15370,7 @@
       </c>
       <c r="D747" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — bd_platform/advanced_ta_risk_layer.py</t>
+          <t>مبني وشغال فعليًا — bd_platform.advanced_ta_risk_layer.compute_volume_profile_poc_123</t>
         </is>
       </c>
     </row>
@@ -15390,7 +15390,7 @@
       </c>
       <c r="D748" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — billing_service.py + billing/subscription_engine.py</t>
+          <t>مبني وشغال فعليًا — billing_service.billing_status</t>
         </is>
       </c>
     </row>
@@ -15410,7 +15410,7 @@
       </c>
       <c r="D749" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — trust_compounding.py — تحقق عميق (كان: إشارات فقط)</t>
+          <t>مبني وشغال فعليًا — trust_compounding.build_evidence_pack</t>
         </is>
       </c>
     </row>
@@ -15430,7 +15430,7 @@
       </c>
       <c r="D750" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — bd_platform/advanced_ta_risk_layer.py</t>
+          <t>مبني وشغال فعليًا — bd_platform.advanced_ta_risk_layer.compute_volume_profile_poc_123</t>
         </is>
       </c>
     </row>
@@ -15470,7 +15470,7 @@
       </c>
       <c r="D752" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — bd_platform/advanced_ta_risk_layer.py</t>
+          <t>مبني وشغال فعليًا — bd_platform.advanced_ta_risk_layer.compute_volume_profile_poc_123</t>
         </is>
       </c>
     </row>
@@ -15530,7 +15530,7 @@
       </c>
       <c r="D755" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — docs/ops/INCIDENT_RESPONSE.md + data/institutional_assurance/incident_response.json</t>
+          <t>مبني وشغال فعليًا — docs/ops/INCIDENT_RESPONSE.md + institutional_assurance/incident_response.json</t>
         </is>
       </c>
     </row>
@@ -15550,7 +15550,7 @@
       </c>
       <c r="D756" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — bd_platform/whales_institutional_layer.py</t>
+          <t>مبني وشغال فعليًا — bd_platform.whales_institutional_layer.build_unified_portfolio_view_81</t>
         </is>
       </c>
     </row>
@@ -15570,7 +15570,7 @@
       </c>
       <c r="D757" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — institutional_assurance.py + uptime_probe_loop + centralized logs</t>
+          <t>مبني وشغال فعليًا — institutional_assurance.get_signed_capacity</t>
         </is>
       </c>
     </row>
@@ -15590,7 +15590,7 @@
       </c>
       <c r="D758" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — institutional_assurance.py + uptime_probe_loop + centralized logs</t>
+          <t>مبني وشغال فعليًا — institutional_assurance.get_signed_capacity</t>
         </is>
       </c>
     </row>
@@ -15610,7 +15610,7 @@
       </c>
       <c r="D759" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — bd_platform/infra_intelligence_layer.py</t>
+          <t>مبني وشغال فعليًا — bd_platform.infra_intelligence_layer.build_admin_analytics_dashboard_95</t>
         </is>
       </c>
     </row>
@@ -15650,7 +15650,7 @@
       </c>
       <c r="D761" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — bd_platform/advanced_ta_risk_layer.py</t>
+          <t>مبني وشغال فعليًا — bd_platform.advanced_ta_risk_layer.compute_volume_profile_poc_123</t>
         </is>
       </c>
     </row>
@@ -15670,7 +15670,7 @@
       </c>
       <c r="D762" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — bd_platform/security_trust_data_layer.py</t>
+          <t>مبني وشغال فعليًا — bd_platform.security_trust_data_layer.build_kill_rate_widget_253</t>
         </is>
       </c>
     </row>
@@ -15690,7 +15690,7 @@
       </c>
       <c r="D763" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — platform_api.py</t>
+          <t>مبني وشغال فعليًا — bd_platform.onchain_platform_layer.run_onchain_platform_e2e_129_139 via platform_api/portfolio/stress-alert</t>
         </is>
       </c>
     </row>
@@ -15710,7 +15710,7 @@
       </c>
       <c r="D764" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — bd_platform/whales_institutional_layer.py</t>
+          <t>مبني وشغال فعليًا — bd_platform.whales_institutional_layer.build_unified_portfolio_view_81</t>
         </is>
       </c>
     </row>
@@ -15750,7 +15750,7 @@
       </c>
       <c r="D766" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — dashboard.py</t>
+          <t>مبني وشغال فعليًا — dashboard.health</t>
         </is>
       </c>
     </row>
@@ -15770,7 +15770,7 @@
       </c>
       <c r="D767" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — enterprise_sso.py + org_rbac.py + admin_mfa.py</t>
+          <t>مبني وشغال فعليًا — enterprise_sso.build_sso_authorize_url_async</t>
         </is>
       </c>
     </row>
@@ -15790,7 +15790,7 @@
       </c>
       <c r="D768" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — bd_platform/pro_trader_layer.py</t>
+          <t>مبني وشغال فعليًا — bd_platform.pro_trader_layer.build_whale_narrative_71</t>
         </is>
       </c>
     </row>
@@ -15850,7 +15850,7 @@
       </c>
       <c r="D771" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — enterprise_sso.py + org_rbac.py + admin_mfa.py</t>
+          <t>مبني وشغال فعليًا — enterprise_sso.build_sso_authorize_url_async</t>
         </is>
       </c>
     </row>
@@ -15870,7 +15870,7 @@
       </c>
       <c r="D772" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — bd_platform/market_analysis_layer.py</t>
+          <t>مبني وشغال فعليًا — bd_platform.market_analysis_layer.compute_whale_retail_ratio_107</t>
         </is>
       </c>
     </row>
@@ -15890,7 +15890,7 @@
       </c>
       <c r="D773" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — bd_platform/data_sources_layer.py</t>
+          <t>مبني وشغال فعليًا — bd_platform.data_sources_layer.compute_opportunity_score_150</t>
         </is>
       </c>
     </row>
@@ -15910,7 +15910,7 @@
       </c>
       <c r="D774" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — platform_api.py + graphql_schema.py + mcp references</t>
+          <t>مبني وشغال فعليًا — graphql_schema.graphql_health</t>
         </is>
       </c>
     </row>
@@ -15930,7 +15930,7 @@
       </c>
       <c r="D775" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — dashboard.py</t>
+          <t>مبني وشغال فعليًا — dashboard.health</t>
         </is>
       </c>
     </row>
@@ -15970,7 +15970,7 @@
       </c>
       <c r="D777" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — bd_platform/advanced_ta_risk_layer.py</t>
+          <t>مبني وشغال فعليًا — bd_platform.advanced_ta_risk_layer.compute_volume_profile_poc_123</t>
         </is>
       </c>
     </row>
@@ -15990,7 +15990,7 @@
       </c>
       <c r="D778" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — dashboard.py</t>
+          <t>مبني وشغال فعليًا — dashboard.health</t>
         </is>
       </c>
     </row>
@@ -16030,7 +16030,7 @@
       </c>
       <c r="D780" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — bd_platform/onchain_defi_sources_layer.py</t>
+          <t>مبني وشغال فعليًا — bd_platform.onchain_defi_sources_layer.run_onchain_defi_sources_e2e_204_216</t>
         </is>
       </c>
     </row>
@@ -16050,7 +16050,7 @@
       </c>
       <c r="D781" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — bd_platform/whales_institutional_layer.py</t>
+          <t>مبني وشغال فعليًا — bd_platform.whales_institutional_layer.build_unified_portfolio_view_81</t>
         </is>
       </c>
     </row>
@@ -16090,7 +16090,7 @@
       </c>
       <c r="D783" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — bd_platform/risk_infrastructure_layer.py</t>
+          <t>مبني وشغال فعليًا — bd_platform.risk_infrastructure_layer.compute_oi_momentum_delta_170</t>
         </is>
       </c>
     </row>
@@ -16130,7 +16130,7 @@
       </c>
       <c r="D785" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — secrets_vault.py Fernet + bd_platform/vault_client.py (ليس HSM)</t>
+          <t>مبني وشغال فعليًا — secrets_vault.get_vault_key</t>
         </is>
       </c>
     </row>
@@ -16150,7 +16150,7 @@
       </c>
       <c r="D786" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — secrets_vault.py Fernet + bd_platform/vault_client.py (ليس HSM)</t>
+          <t>مبني وشغال فعليًا — secrets_vault.get_vault_key</t>
         </is>
       </c>
     </row>
@@ -16170,7 +16170,7 @@
       </c>
       <c r="D787" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — platform_api.py</t>
+          <t>مبني وشغال فعليًا — platform_api.drawdown_status</t>
         </is>
       </c>
     </row>
@@ -16190,7 +16190,7 @@
       </c>
       <c r="D788" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — pentest_attestation.py (قالب؛ verify_pentest_attestation=False)</t>
+          <t>مبني وشغال فعليًا — pentest_attestation.get_pentest_attestation</t>
         </is>
       </c>
     </row>
@@ -16210,7 +16210,7 @@
       </c>
       <c r="D789" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — cap646/handlers/institutional.py — security-first institutional surfaces</t>
+          <t>مبني وشغال فعليًا — cap646.handlers.institutional.handle_institutional_capability</t>
         </is>
       </c>
     </row>
@@ -16230,7 +16230,7 @@
       </c>
       <c r="D790" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — platform_api.py</t>
+          <t>مبني وشغال فعليًا — bd_platform.onchain_defi_sources_layer.capital_allocation_insight_213 via platform_api/portfolio/capital-allocation</t>
         </is>
       </c>
     </row>
@@ -16290,7 +16290,7 @@
       </c>
       <c r="D793" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — data_provenance_score.py + blackdark/data/provenance.py (لا visualization)</t>
+          <t>مبني وشغال فعليًا — data_provenance_score.compute_data_provenance_score</t>
         </is>
       </c>
     </row>
@@ -16310,7 +16310,7 @@
       </c>
       <c r="D794" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — institutional_commerce.py + legal_commercial_layer evaluate_aml_gate_59</t>
+          <t>مبني وشغال فعليًا — bd_platform.legal_commercial_layer.evaluate_aml_gate_59</t>
         </is>
       </c>
     </row>
@@ -16330,7 +16330,7 @@
       </c>
       <c r="D795" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — data_provenance_score.py + blackdark/data/provenance.py (لا visualization)</t>
+          <t>مبني وشغال فعليًا — data_provenance_score.compute_data_provenance_score</t>
         </is>
       </c>
     </row>
@@ -16350,7 +16350,7 @@
       </c>
       <c r="D796" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — dashboard.py</t>
+          <t>مبني وشغال فعليًا — dashboard.health</t>
         </is>
       </c>
     </row>
@@ -16370,7 +16370,7 @@
       </c>
       <c r="D797" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — platform_api.py</t>
+          <t>مبني وشغال فعليًا — bd_platform.whales_institutional_layer.analyze_wallet_surveillance_79 via platform_api/oracle/on-chain/surveillance</t>
         </is>
       </c>
     </row>
@@ -16390,7 +16390,7 @@
       </c>
       <c r="D798" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — bd_platform/infra_intelligence_layer.py</t>
+          <t>مبني وشغال فعليًا — bd_platform.infra_intelligence_layer.build_admin_analytics_dashboard_95</t>
         </is>
       </c>
     </row>
@@ -16410,7 +16410,7 @@
       </c>
       <c r="D799" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — platform_api.py</t>
+          <t>مبني وشغال فعليًا — bd_platform.onchain_platform_layer.scan_flash_loan_vulnerabilities_132 via platform_api/oracle/on-chain/security/flash-loan-scan</t>
         </is>
       </c>
     </row>
@@ -16430,7 +16430,7 @@
       </c>
       <c r="D800" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — platform_api.py</t>
+          <t>مبني وشغال فعليًا — bd_platform.whales_institutional_layer.build_performance_ledger_view_84 via platform_api/transparency/performance</t>
         </is>
       </c>
     </row>
@@ -16450,7 +16450,7 @@
       </c>
       <c r="D801" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — platform_api.py</t>
+          <t>مبني وشغال فعليًا — platform_api.drawdown_status</t>
         </is>
       </c>
     </row>
@@ -16470,7 +16470,7 @@
       </c>
       <c r="D802" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — bd_platform/institutional_b2b_layer.py + b2b_websocket_hub.py</t>
+          <t>مبني وشغال فعليًا — bd_platform.institutional_b2b_layer.build_ic_report_87</t>
         </is>
       </c>
     </row>
@@ -16530,7 +16530,7 @@
       </c>
       <c r="D805" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — bd_platform/derivatives_ta_research_layer.py</t>
+          <t>مبني وشغال فعليًا — bd_platform.derivatives_ta_research_layer.compute_cvd_194</t>
         </is>
       </c>
     </row>
@@ -16550,7 +16550,7 @@
       </c>
       <c r="D806" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — docs/ops/INCIDENT_RESPONSE.md + institutional_assurance incident_response.json</t>
+          <t>مبني وشغال فعليًا — docs/ops/INCIDENT_RESPONSE.md + institutional_assurance/incident_response.json</t>
         </is>
       </c>
     </row>
@@ -16570,7 +16570,7 @@
       </c>
       <c r="D807" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — dashboard.py</t>
+          <t>مبني وشغال فعليًا — dashboard.health</t>
         </is>
       </c>
     </row>
@@ -16590,7 +16590,7 @@
       </c>
       <c r="D808" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — enterprise_sso.py + org_rbac.py + admin_mfa.py</t>
+          <t>مبني وشغال فعليًا — enterprise_sso.build_sso_authorize_url_async</t>
         </is>
       </c>
     </row>
@@ -16610,7 +16610,7 @@
       </c>
       <c r="D809" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — scripts/load_test*.py + scale_readiness.py (آخر run 2026-08-12)</t>
+          <t>مبني وشغال فعليًا — scale_readiness.scale_readiness_report</t>
         </is>
       </c>
     </row>
@@ -16630,7 +16630,7 @@
       </c>
       <c r="D810" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — dashboard.py I DON'T KNOW dead-zone + constitution_gates (ليس محرك epistemic مستقل)</t>
+          <t>مبني وشغال فعليًا — dashboard.health</t>
         </is>
       </c>
     </row>
@@ -16650,7 +16650,7 @@
       </c>
       <c r="D811" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — enterprise_sso.py + org_rbac.py (SSO/RBAC جزئي؛ ليس IdP enterprise كامل)</t>
+          <t>مبني وشغال فعليًا — enterprise_sso.build_sso_authorize_url_async</t>
         </is>
       </c>
     </row>
@@ -16670,7 +16670,7 @@
       </c>
       <c r="D812" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — gdpr_service.py + legal_commercial_layer gdpr_compliance_status_58</t>
+          <t>مبني وشغال فعليًا — bd_platform.legal_commercial_layer.gdpr_compliance_status_58</t>
         </is>
       </c>
     </row>
@@ -16710,7 +16710,7 @@
       </c>
       <c r="D814" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — constitution_gates.py + dimension_conflict_guard (شروط إبطال جزئية)</t>
+          <t>مبني وشغال فعليًا — constitution_gates.ensure_execution_gates</t>
         </is>
       </c>
     </row>
@@ -16870,7 +16870,7 @@
       </c>
       <c r="D822" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — didit_kyc.py</t>
+          <t>مبني وشغال فعليًا — didit_kyc.didit_status</t>
         </is>
       </c>
     </row>
@@ -16890,7 +16890,7 @@
       </c>
       <c r="D823" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — bd_platform/finbert_sentiment.py</t>
+          <t>مبني وشغال فعليًا — bd_platform.finbert_sentiment.analyze_text</t>
         </is>
       </c>
     </row>
@@ -16950,7 +16950,7 @@
       </c>
       <c r="D826" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — lp_il_simulator.py</t>
+          <t>مبني وشغال فعليًا — lp_il_simulator.compute_impermanent_loss_pct</t>
         </is>
       </c>
     </row>
@@ -16970,7 +16970,7 @@
       </c>
       <c r="D827" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — glass_box_challenge.py</t>
+          <t>مبني وشغال فعليًا — glass_box_challenge.build_glass_box_operator_pack</t>
         </is>
       </c>
     </row>

--- a/capabilities_checklist_completed.xlsx
+++ b/capabilities_checklist_completed.xlsx
@@ -490,7 +490,7 @@
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — trade_simulator.py + grid_bot.py (paper/sim only; لا محرك paper-trading broker حقيقي)</t>
+          <t>مبني وشغال فعليًا — trade_simulator.simulate_spot_trade</t>
         </is>
       </c>
     </row>
@@ -810,7 +810,7 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — alert_service.py + instant_alert_engine.py (لا orchestrator مستقل)</t>
+          <t>مبني وشغال فعليًا — bd_platform.alert_orchestration.alert_orchestration_status_18</t>
         </is>
       </c>
     </row>
@@ -1030,7 +1030,7 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — bd_platform/retail_intelligence_layer.py</t>
+          <t>مبني وشغال فعليًا — bd_platform.retail_intelligence_layer.compare_discipline_66</t>
         </is>
       </c>
     </row>
@@ -1070,7 +1070,7 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — bd_platform/retail_intelligence_layer.py</t>
+          <t>مبني وشغال فعليًا — bd_platform.retail_intelligence_layer.build_discipline_tab_66</t>
         </is>
       </c>
     </row>
@@ -1430,7 +1430,7 @@
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — risk_manager + drawdown_guard (حماية؛ ليس flash-crash engine مخصص بالكامل)</t>
+          <t>مبني وشغال فعليًا — bd_platform.flash_crash_protection.flash_crash_protection_status_49</t>
         </is>
       </c>
     </row>
@@ -5850,7 +5850,7 @@
       </c>
       <c r="D271" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — bd_platform/retail_intelligence_layer.py</t>
+          <t>مبني وشغال فعليًا — bd_platform.free_integrations.holder_analytics</t>
         </is>
       </c>
     </row>
@@ -6210,7 +6210,7 @@
       </c>
       <c r="D289" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — bd_platform/correlation_mindshare.py</t>
+          <t>مبني وشغال فعليًا — bd_platform.correlation_mindshare.compute_mindshare_correlation_288</t>
         </is>
       </c>
     </row>
@@ -6770,7 +6770,7 @@
       </c>
       <c r="D317" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — bd_platform/sse_stream.py</t>
+          <t>مبني وشغال فعليًا — bd_platform.sse_stream.sse_digest_status_316</t>
         </is>
       </c>
     </row>
@@ -7070,7 +7070,7 @@
       </c>
       <c r="D332" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — i18n_locales.py — تحقق عميق (كان: إشارات فقط)</t>
+          <t>مبني وشغال فعليًا — bd_platform.intelligence_analysis_layer.analyze_arbitrage_opportunity_153</t>
         </is>
       </c>
     </row>
@@ -8010,7 +8010,7 @@
       </c>
       <c r="D379" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — bd_platform/retail_intelligence_layer.py</t>
+          <t>مبني وشغال فعليًا — exchange_currency_status.deposit_currencies_open</t>
         </is>
       </c>
     </row>
@@ -8030,7 +8030,7 @@
       </c>
       <c r="D380" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — bd_platform/retail_intelligence_layer.py</t>
+          <t>مبني وشغال فعليًا — bd_platform.arbitrage_portfolio_ux_layer.analyze_liquidity_capacity_189</t>
         </is>
       </c>
     </row>
@@ -8250,7 +8250,7 @@
       </c>
       <c r="D391" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — i18n_locales.py — تحقق عميق (كان: إشارات فقط)</t>
+          <t>مبني وشغال فعليًا — bd_platform.whales_institutional_layer.build_exchange_health_80</t>
         </is>
       </c>
     </row>
@@ -8310,7 +8310,7 @@
       </c>
       <c r="D394" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — scripts/build_capabilities_checklist.py — تحقق عميق (كان: إشارات فقط)</t>
+          <t>مبني وشغال فعليًا — data_sources_registry.registry_summary</t>
         </is>
       </c>
     </row>
@@ -8370,7 +8370,7 @@
       </c>
       <c r="D397" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — scripts/build_capabilities_checklist.py — تحقق عميق (كان: إشارات فقط)</t>
+          <t>مبني وشغال فعليًا — bd_platform.news_classifier.coindesk_feed</t>
         </is>
       </c>
     </row>
@@ -8630,7 +8630,7 @@
       </c>
       <c r="D410" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — news_classifier + intelligence layers (feed؛ ليس منتج QuickTake كامل)</t>
+          <t>مبني وشغال فعليًا — bd_platform.quicktake_feed.quicktake_feed_status_409</t>
         </is>
       </c>
     </row>
@@ -10790,7 +10790,7 @@
       </c>
       <c r="D518" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — setup_telegram.py — تحقق عميق (كان: إشارات فقط)</t>
+          <t>مبني وشغال فعليًا — comparison_engine.run_comparison_engine</t>
         </is>
       </c>
     </row>
@@ -11010,7 +11010,7 @@
       </c>
       <c r="D529" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — institutional handler surfaces</t>
+          <t>مبني وشغال فعليًا — bd_platform.market_rankings.market_rankings</t>
         </is>
       </c>
     </row>
@@ -13050,7 +13050,7 @@
       </c>
       <c r="D631" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — bd_platform/retail_intelligence_layer.py</t>
+          <t>مبني وشغال فعليًا — bd_platform.intelligence_ux_extensions_layer.scan_market_opportunities_238</t>
         </is>
       </c>
     </row>
@@ -14310,7 +14310,7 @@
       </c>
       <c r="D694" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — bd_platform/oneinch_connector.py</t>
+          <t>مبني جزئيًا — EXTERNAL_BLOCKED — Polygon.io API license requires human vendor contract; proxy: bd_platform/oneinch_connector.py</t>
         </is>
       </c>
     </row>
@@ -14490,7 +14490,7 @@
       </c>
       <c r="D703" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — mcp server references + graphql_schema (جزئي)</t>
+          <t>مبني وشغال فعليًا — graphql_schema.graphql_health</t>
         </is>
       </c>
     </row>
@@ -15350,7 +15350,7 @@
       </c>
       <c r="D746" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — subscription_analytics.py + billing analytics (ليس visitor counter كامل)</t>
+          <t>مبني وشغال فعليًا — subscription_analytics.subscription_analytics_status_745</t>
         </is>
       </c>
     </row>
@@ -15490,7 +15490,7 @@
       </c>
       <c r="D753" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — i18n_locales.py — تحقق عميق (كان: إشارات فقط)</t>
+          <t>مبني وشغال فعليًا — institutional_assurance.backup_status</t>
         </is>
       </c>
     </row>
@@ -15510,7 +15510,7 @@
       </c>
       <c r="D754" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — i18n_locales.py — تحقق عميق (كان: إشارات فقط)</t>
+          <t>مبني وشغال فعليًا — institutional_assurance.ir_program</t>
         </is>
       </c>
     </row>
@@ -16770,7 +16770,7 @@
       </c>
       <c r="D817" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — dimension_conflict_guard abstain/veto + ml/drift_monitor OOD fail-closed</t>
+          <t>مبني وشغال فعليًا — dimension_conflict_guard.dimension_conflict_status</t>
         </is>
       </c>
     </row>
@@ -16830,7 +16830,7 @@
       </c>
       <c r="D820" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — blackdark/data/</t>
+          <t>مبني وشغال فعليًا — blackdark.data.db.data_engine_available</t>
         </is>
       </c>
     </row>
